--- a/saidas/painel_meliuz.xlsx
+++ b/saidas/painel_meliuz.xlsx
@@ -264,7 +264,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
+  <style val="11"/>
   <chart>
     <title>
       <tx>
@@ -309,6 +309,9 @@
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <showVal val="0"/>
+        </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -345,114 +348,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Lucro liquido</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Margem e ROI por grupo</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Parceiro_C'!F11</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Parceiro_C'!$A$12:$A$13</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Parceiro_C'!$F$12:$F$13</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Parceiro_C'!G11</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Parceiro_C'!$A$12:$A$13</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Parceiro_C'!$G$12:$G$13</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
         <title>
           <tx>
             <rich>
@@ -470,199 +365,30 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>%</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Lucro liquido diario por grupo</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Parceiro_C'!B34</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Parceiro_C'!$A$35:$A$79</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Parceiro_C'!$B$35:$B$79</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Parceiro_C'!C34</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Parceiro_C'!$A$35:$A$79</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Parceiro_C'!$C$35:$C$79</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Data</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Lucro liquido</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
+  <spPr>
+    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
+  <style val="12"/>
   <chart>
     <title>
       <tx>
@@ -707,6 +433,9 @@
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <showVal val="0"/>
+        </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -743,7 +472,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -753,7 +481,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>ROI</a:t>
+                  <a:t/>
                 </a:r>
               </a:p>
             </rich>
@@ -763,16 +491,28 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
+  <style val="11"/>
   <chart>
     <title>
       <tx>
@@ -817,6 +557,9 @@
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <showVal val="0"/>
+        </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -853,7 +596,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -863,7 +605,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>R$</a:t>
+                  <a:t/>
                 </a:r>
               </a:p>
             </rich>
@@ -873,16 +615,28 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
+  <style val="12"/>
   <chart>
     <title>
       <tx>
@@ -893,7 +647,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Margem e ROI por grupo</a:t>
+              <a:t>ROI de cashback por grupo</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -906,30 +660,6 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Parceiro_A'!F11</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Parceiro_A'!$A$12:$A$14</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Parceiro_A'!$F$12:$F$14</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
           <tx>
             <strRef>
               <f>'Parceiro_A'!G11</f>
@@ -951,6 +681,9 @@
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <showVal val="0"/>
+        </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -987,7 +720,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -997,7 +729,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>%</a:t>
+                  <a:t/>
                 </a:r>
               </a:p>
             </rich>
@@ -1007,202 +739,28 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Lucro liquido diario por grupo</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Parceiro_A'!B34</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Parceiro_A'!$A$35:$A$126</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Parceiro_A'!$B$35:$B$126</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Parceiro_A'!C34</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Parceiro_A'!$A$35:$A$126</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Parceiro_A'!$C$35:$C$126</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'Parceiro_A'!D34</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Parceiro_A'!$A$35:$A$126</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Parceiro_A'!$D$35:$D$126</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Data</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Lucro liquido</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
+  <style val="11"/>
   <chart>
     <title>
       <tx>
@@ -1247,6 +805,9 @@
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <showVal val="0"/>
+        </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -1283,7 +844,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -1293,7 +853,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>R$</a:t>
+                  <a:t/>
                 </a:r>
               </a:p>
             </rich>
@@ -1303,16 +863,28 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
+  <style val="12"/>
   <chart>
     <title>
       <tx>
@@ -1323,7 +895,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Margem e ROI por grupo</a:t>
+              <a:t>ROI de cashback por grupo</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1336,30 +908,6 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Parceiro_B'!F11</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Parceiro_B'!$A$12:$A$14</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Parceiro_B'!$F$12:$F$14</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
           <tx>
             <strRef>
               <f>'Parceiro_B'!G11</f>
@@ -1381,6 +929,9 @@
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <showVal val="0"/>
+        </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -1417,7 +968,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -1427,7 +977,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>%</a:t>
+                  <a:t/>
                 </a:r>
               </a:p>
             </rich>
@@ -1437,202 +987,28 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Lucro liquido diario por grupo</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Parceiro_B'!B34</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Parceiro_B'!$A$35:$A$95</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Parceiro_B'!$B$35:$B$95</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Parceiro_B'!C34</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Parceiro_B'!$A$35:$A$95</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Parceiro_B'!$C$35:$C$95</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'Parceiro_B'!D34</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Parceiro_B'!$A$35:$A$95</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Parceiro_B'!$D$35:$D$95</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Data</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Lucro liquido</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
+  <style val="11"/>
   <chart>
     <title>
       <tx>
@@ -1677,6 +1053,9 @@
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <showVal val="0"/>
+        </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -1713,7 +1092,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -1723,7 +1101,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>R$</a:t>
+                  <a:t/>
                 </a:r>
               </a:p>
             </rich>
@@ -1733,10 +1111,146 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>ROI de cashback por grupo</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Parceiro_C'!G11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Parceiro_C'!$A$12:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Parceiro_C'!$G$12:$G$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="0"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1746,10 +1260,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="3240000"/>
+    <ext cx="5400000" cy="2808000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1768,10 +1282,10 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="3240000"/>
+    <ext cx="5400000" cy="2808000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1795,10 +1309,10 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5040000" cy="3240000"/>
+    <ext cx="5040000" cy="2736000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1817,10 +1331,10 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5040000" cy="3240000"/>
+    <ext cx="5040000" cy="2736000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1835,28 +1349,6 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6480000" cy="3600000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1866,10 +1358,10 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5040000" cy="3240000"/>
+    <ext cx="5040000" cy="2736000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1888,10 +1380,10 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5040000" cy="3240000"/>
+    <ext cx="5040000" cy="2736000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1906,28 +1398,6 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6480000" cy="3600000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1937,10 +1407,10 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5040000" cy="3240000"/>
+    <ext cx="5040000" cy="2736000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1959,10 +1429,10 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5040000" cy="3240000"/>
+    <ext cx="5040000" cy="2736000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1972,28 +1442,6 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6480000" cy="3600000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -5819,7 +5267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z126"/>
+  <dimension ref="A1:Z120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6697,7 +6145,11 @@
       <c r="Z26" s="3" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="3" t="n"/>
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>Dados diarios para auditoria</t>
+        </is>
+      </c>
       <c r="B27" s="3" t="n"/>
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="n"/>
@@ -6725,10 +6177,26 @@
       <c r="Z27" s="3" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="3" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="n"/>
       <c r="G28" s="3" t="n"/>
@@ -6753,10 +6221,20 @@
       <c r="Z28" s="3" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="3" t="n"/>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="n">
+        <v>7006</v>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>6475</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>4794</v>
+      </c>
       <c r="E29" s="3" t="n"/>
       <c r="F29" s="3" t="n"/>
       <c r="G29" s="3" t="n"/>
@@ -6781,10 +6259,20 @@
       <c r="Z29" s="3" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="3" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>2011-01-02</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="n">
+        <v>5495</v>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>3669</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>2266</v>
+      </c>
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="n"/>
       <c r="G30" s="3" t="n"/>
@@ -6809,10 +6297,20 @@
       <c r="Z30" s="3" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="3" t="n"/>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>2011-01-03</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="n">
+        <v>3481</v>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>3875</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>3011</v>
+      </c>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n"/>
       <c r="G31" s="3" t="n"/>
@@ -6837,10 +6335,20 @@
       <c r="Z31" s="3" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="3" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>2011-01-04</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n">
+        <v>7512</v>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>5297</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>3356</v>
+      </c>
       <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="n"/>
       <c r="G32" s="3" t="n"/>
@@ -6865,14 +6373,20 @@
       <c r="Z32" s="3" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>Dados diarios para auditoria</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>2011-01-05</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="n">
+        <v>8167</v>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>7124</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>3628</v>
+      </c>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="n"/>
       <c r="G33" s="3" t="n"/>
@@ -6897,25 +6411,19 @@
       <c r="Z33" s="3" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>Grupo 1</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>Grupo 2</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>Grupo 3</t>
-        </is>
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>2011-01-06</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>8134</v>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>6855</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>3556</v>
       </c>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n"/>
@@ -6943,17 +6451,17 @@
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>2011-01-01</t>
+          <t>2011-01-07</t>
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>7006</v>
+        <v>7776</v>
       </c>
       <c r="C35" s="12" t="n">
-        <v>6475</v>
+        <v>6999</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>4794</v>
+        <v>3598</v>
       </c>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n"/>
@@ -6981,17 +6489,17 @@
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>2011-01-02</t>
+          <t>2011-01-08</t>
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>5495</v>
+        <v>10448</v>
       </c>
       <c r="C36" s="12" t="n">
-        <v>3669</v>
+        <v>8078</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>2266</v>
+        <v>5819</v>
       </c>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="n"/>
@@ -7019,17 +6527,17 @@
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>2011-01-03</t>
+          <t>2011-01-09</t>
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>3481</v>
+        <v>3872</v>
       </c>
       <c r="C37" s="12" t="n">
-        <v>3875</v>
+        <v>3528</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>3011</v>
+        <v>2191</v>
       </c>
       <c r="E37" s="3" t="n"/>
       <c r="F37" s="3" t="n"/>
@@ -7057,17 +6565,17 @@
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>2011-01-04</t>
+          <t>2011-01-10</t>
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>7512</v>
+        <v>5178</v>
       </c>
       <c r="C38" s="12" t="n">
-        <v>5297</v>
+        <v>4039</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>3356</v>
+        <v>3435</v>
       </c>
       <c r="E38" s="3" t="n"/>
       <c r="F38" s="3" t="n"/>
@@ -7095,17 +6603,17 @@
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>2011-01-05</t>
+          <t>2011-01-11</t>
         </is>
       </c>
       <c r="B39" s="12" t="n">
-        <v>8167</v>
+        <v>9499</v>
       </c>
       <c r="C39" s="12" t="n">
-        <v>7124</v>
+        <v>7324</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>3628</v>
+        <v>4845</v>
       </c>
       <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="n"/>
@@ -7133,17 +6641,17 @@
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>2011-01-06</t>
+          <t>2011-01-12</t>
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>8134</v>
+        <v>7006</v>
       </c>
       <c r="C40" s="12" t="n">
-        <v>6855</v>
+        <v>5934</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>3556</v>
+        <v>4546</v>
       </c>
       <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="n"/>
@@ -7171,17 +6679,17 @@
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>2011-01-07</t>
+          <t>2011-01-13</t>
         </is>
       </c>
       <c r="B41" s="12" t="n">
-        <v>7776</v>
+        <v>14785</v>
       </c>
       <c r="C41" s="12" t="n">
-        <v>6999</v>
+        <v>12703</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>3598</v>
+        <v>6912</v>
       </c>
       <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="n"/>
@@ -7209,17 +6717,17 @@
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>2011-01-08</t>
+          <t>2011-01-14</t>
         </is>
       </c>
       <c r="B42" s="12" t="n">
-        <v>10448</v>
+        <v>13428</v>
       </c>
       <c r="C42" s="12" t="n">
-        <v>8078</v>
+        <v>8198</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>5819</v>
+        <v>5500</v>
       </c>
       <c r="E42" s="3" t="n"/>
       <c r="F42" s="3" t="n"/>
@@ -7247,17 +6755,17 @@
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>2011-01-09</t>
+          <t>2011-01-15</t>
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>3872</v>
+        <v>6041</v>
       </c>
       <c r="C43" s="12" t="n">
-        <v>3528</v>
+        <v>4889</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>2191</v>
+        <v>2504</v>
       </c>
       <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="n"/>
@@ -7285,17 +6793,17 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>2011-01-10</t>
+          <t>2011-01-16</t>
         </is>
       </c>
       <c r="B44" s="12" t="n">
-        <v>5178</v>
+        <v>4451</v>
       </c>
       <c r="C44" s="12" t="n">
-        <v>4039</v>
+        <v>2989</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>3435</v>
+        <v>2133</v>
       </c>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
@@ -7323,17 +6831,17 @@
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>2011-01-11</t>
+          <t>2011-01-17</t>
         </is>
       </c>
       <c r="B45" s="12" t="n">
-        <v>9499</v>
+        <v>4584</v>
       </c>
       <c r="C45" s="12" t="n">
-        <v>7324</v>
+        <v>4143</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>4845</v>
+        <v>1969</v>
       </c>
       <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="n"/>
@@ -7361,17 +6869,17 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>2011-01-12</t>
+          <t>2011-01-18</t>
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>7006</v>
+        <v>7297</v>
       </c>
       <c r="C46" s="12" t="n">
-        <v>5934</v>
+        <v>7790</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>4546</v>
+        <v>4048</v>
       </c>
       <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="n"/>
@@ -7399,17 +6907,17 @@
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>2011-01-13</t>
+          <t>2011-01-19</t>
         </is>
       </c>
       <c r="B47" s="12" t="n">
-        <v>14785</v>
+        <v>6641</v>
       </c>
       <c r="C47" s="12" t="n">
-        <v>12703</v>
+        <v>7202</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>6912</v>
+        <v>3642</v>
       </c>
       <c r="E47" s="3" t="n"/>
       <c r="F47" s="3" t="n"/>
@@ -7437,17 +6945,17 @@
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>2011-01-14</t>
+          <t>2011-01-20</t>
         </is>
       </c>
       <c r="B48" s="12" t="n">
-        <v>13428</v>
+        <v>8809</v>
       </c>
       <c r="C48" s="12" t="n">
-        <v>8198</v>
+        <v>6225</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>5500</v>
+        <v>3737</v>
       </c>
       <c r="E48" s="3" t="n"/>
       <c r="F48" s="3" t="n"/>
@@ -7475,17 +6983,17 @@
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>2011-01-15</t>
+          <t>2011-01-21</t>
         </is>
       </c>
       <c r="B49" s="12" t="n">
-        <v>6041</v>
+        <v>4179</v>
       </c>
       <c r="C49" s="12" t="n">
-        <v>4889</v>
+        <v>3549</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>2504</v>
+        <v>2368</v>
       </c>
       <c r="E49" s="3" t="n"/>
       <c r="F49" s="3" t="n"/>
@@ -7513,17 +7021,17 @@
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>2011-01-16</t>
+          <t>2011-01-22</t>
         </is>
       </c>
       <c r="B50" s="12" t="n">
-        <v>4451</v>
+        <v>3425</v>
       </c>
       <c r="C50" s="12" t="n">
-        <v>2989</v>
+        <v>3794</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>2133</v>
+        <v>2099</v>
       </c>
       <c r="E50" s="3" t="n"/>
       <c r="F50" s="3" t="n"/>
@@ -7551,17 +7059,17 @@
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>2011-01-17</t>
+          <t>2011-01-23</t>
         </is>
       </c>
       <c r="B51" s="12" t="n">
-        <v>4584</v>
+        <v>2531</v>
       </c>
       <c r="C51" s="12" t="n">
-        <v>4143</v>
+        <v>1918</v>
       </c>
       <c r="D51" s="12" t="n">
-        <v>1969</v>
+        <v>2022</v>
       </c>
       <c r="E51" s="3" t="n"/>
       <c r="F51" s="3" t="n"/>
@@ -7589,17 +7097,17 @@
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>2011-01-18</t>
+          <t>2011-01-24</t>
         </is>
       </c>
       <c r="B52" s="12" t="n">
-        <v>7297</v>
+        <v>3340</v>
       </c>
       <c r="C52" s="12" t="n">
-        <v>7790</v>
+        <v>3533</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>4048</v>
+        <v>1573</v>
       </c>
       <c r="E52" s="3" t="n"/>
       <c r="F52" s="3" t="n"/>
@@ -7627,17 +7135,17 @@
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>2011-01-19</t>
+          <t>2011-01-25</t>
         </is>
       </c>
       <c r="B53" s="12" t="n">
-        <v>6641</v>
+        <v>4575</v>
       </c>
       <c r="C53" s="12" t="n">
-        <v>7202</v>
+        <v>4274</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>3642</v>
+        <v>2038</v>
       </c>
       <c r="E53" s="3" t="n"/>
       <c r="F53" s="3" t="n"/>
@@ -7665,17 +7173,17 @@
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>2011-01-20</t>
+          <t>2011-01-26</t>
         </is>
       </c>
       <c r="B54" s="12" t="n">
-        <v>8809</v>
+        <v>7330</v>
       </c>
       <c r="C54" s="12" t="n">
-        <v>6225</v>
+        <v>6618</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>3737</v>
+        <v>4142</v>
       </c>
       <c r="E54" s="3" t="n"/>
       <c r="F54" s="3" t="n"/>
@@ -7703,17 +7211,17 @@
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>2011-01-21</t>
+          <t>2011-01-27</t>
         </is>
       </c>
       <c r="B55" s="12" t="n">
-        <v>4179</v>
+        <v>6401</v>
       </c>
       <c r="C55" s="12" t="n">
-        <v>3549</v>
+        <v>4478</v>
       </c>
       <c r="D55" s="12" t="n">
-        <v>2368</v>
+        <v>3119</v>
       </c>
       <c r="E55" s="3" t="n"/>
       <c r="F55" s="3" t="n"/>
@@ -7741,17 +7249,17 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>2011-01-22</t>
+          <t>2011-01-28</t>
         </is>
       </c>
       <c r="B56" s="12" t="n">
-        <v>3425</v>
+        <v>4436</v>
       </c>
       <c r="C56" s="12" t="n">
-        <v>3794</v>
+        <v>3084</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>2099</v>
+        <v>2315</v>
       </c>
       <c r="E56" s="3" t="n"/>
       <c r="F56" s="3" t="n"/>
@@ -7779,17 +7287,17 @@
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>2011-01-23</t>
+          <t>2011-01-29</t>
         </is>
       </c>
       <c r="B57" s="12" t="n">
-        <v>2531</v>
+        <v>4322</v>
       </c>
       <c r="C57" s="12" t="n">
-        <v>1918</v>
+        <v>2928</v>
       </c>
       <c r="D57" s="12" t="n">
-        <v>2022</v>
+        <v>1533</v>
       </c>
       <c r="E57" s="3" t="n"/>
       <c r="F57" s="3" t="n"/>
@@ -7817,17 +7325,17 @@
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>2011-01-24</t>
+          <t>2011-01-30</t>
         </is>
       </c>
       <c r="B58" s="12" t="n">
-        <v>3340</v>
+        <v>1760</v>
       </c>
       <c r="C58" s="12" t="n">
-        <v>3533</v>
+        <v>2224</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>1573</v>
+        <v>1198</v>
       </c>
       <c r="E58" s="3" t="n"/>
       <c r="F58" s="3" t="n"/>
@@ -7855,17 +7363,17 @@
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>2011-01-25</t>
+          <t>2011-01-31</t>
         </is>
       </c>
       <c r="B59" s="12" t="n">
-        <v>4575</v>
+        <v>1506</v>
       </c>
       <c r="C59" s="12" t="n">
-        <v>4274</v>
+        <v>2084</v>
       </c>
       <c r="D59" s="12" t="n">
-        <v>2038</v>
+        <v>1014</v>
       </c>
       <c r="E59" s="3" t="n"/>
       <c r="F59" s="3" t="n"/>
@@ -7893,17 +7401,17 @@
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>2011-01-26</t>
+          <t>2011-02-01</t>
         </is>
       </c>
       <c r="B60" s="12" t="n">
-        <v>7330</v>
+        <v>2469</v>
       </c>
       <c r="C60" s="12" t="n">
-        <v>6618</v>
+        <v>2290</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>4142</v>
+        <v>1444</v>
       </c>
       <c r="E60" s="3" t="n"/>
       <c r="F60" s="3" t="n"/>
@@ -7931,17 +7439,17 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>2011-01-27</t>
+          <t>2011-02-02</t>
         </is>
       </c>
       <c r="B61" s="12" t="n">
-        <v>6401</v>
+        <v>2662</v>
       </c>
       <c r="C61" s="12" t="n">
-        <v>4478</v>
+        <v>2726</v>
       </c>
       <c r="D61" s="12" t="n">
-        <v>3119</v>
+        <v>1645</v>
       </c>
       <c r="E61" s="3" t="n"/>
       <c r="F61" s="3" t="n"/>
@@ -7969,17 +7477,17 @@
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>2011-01-28</t>
+          <t>2011-02-03</t>
         </is>
       </c>
       <c r="B62" s="12" t="n">
-        <v>4436</v>
+        <v>3399</v>
       </c>
       <c r="C62" s="12" t="n">
-        <v>3084</v>
+        <v>4480</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>2315</v>
+        <v>2548</v>
       </c>
       <c r="E62" s="3" t="n"/>
       <c r="F62" s="3" t="n"/>
@@ -8007,17 +7515,17 @@
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>2011-01-29</t>
+          <t>2011-02-04</t>
         </is>
       </c>
       <c r="B63" s="12" t="n">
-        <v>4322</v>
+        <v>4248</v>
       </c>
       <c r="C63" s="12" t="n">
-        <v>2928</v>
+        <v>4033</v>
       </c>
       <c r="D63" s="12" t="n">
-        <v>1533</v>
+        <v>3027</v>
       </c>
       <c r="E63" s="3" t="n"/>
       <c r="F63" s="3" t="n"/>
@@ -8045,17 +7553,17 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>2011-01-30</t>
+          <t>2011-02-05</t>
         </is>
       </c>
       <c r="B64" s="12" t="n">
-        <v>1760</v>
+        <v>4895</v>
       </c>
       <c r="C64" s="12" t="n">
-        <v>2224</v>
+        <v>2618</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>1198</v>
+        <v>1971</v>
       </c>
       <c r="E64" s="3" t="n"/>
       <c r="F64" s="3" t="n"/>
@@ -8083,17 +7591,17 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>2011-01-31</t>
+          <t>2011-02-06</t>
         </is>
       </c>
       <c r="B65" s="12" t="n">
-        <v>1506</v>
+        <v>3676</v>
       </c>
       <c r="C65" s="12" t="n">
-        <v>2084</v>
+        <v>2775</v>
       </c>
       <c r="D65" s="12" t="n">
-        <v>1014</v>
+        <v>1548</v>
       </c>
       <c r="E65" s="3" t="n"/>
       <c r="F65" s="3" t="n"/>
@@ -8121,17 +7629,17 @@
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>2011-02-01</t>
+          <t>2011-02-07</t>
         </is>
       </c>
       <c r="B66" s="12" t="n">
-        <v>2469</v>
+        <v>4090</v>
       </c>
       <c r="C66" s="12" t="n">
-        <v>2290</v>
+        <v>3239</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>1444</v>
+        <v>1902</v>
       </c>
       <c r="E66" s="3" t="n"/>
       <c r="F66" s="3" t="n"/>
@@ -8159,17 +7667,17 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>2011-02-02</t>
+          <t>2011-02-08</t>
         </is>
       </c>
       <c r="B67" s="12" t="n">
-        <v>2662</v>
+        <v>5170</v>
       </c>
       <c r="C67" s="12" t="n">
-        <v>2726</v>
+        <v>3553</v>
       </c>
       <c r="D67" s="12" t="n">
-        <v>1645</v>
+        <v>2190</v>
       </c>
       <c r="E67" s="3" t="n"/>
       <c r="F67" s="3" t="n"/>
@@ -8197,17 +7705,17 @@
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>2011-02-03</t>
+          <t>2011-02-09</t>
         </is>
       </c>
       <c r="B68" s="12" t="n">
-        <v>3399</v>
+        <v>5365</v>
       </c>
       <c r="C68" s="12" t="n">
-        <v>4480</v>
+        <v>3887</v>
       </c>
       <c r="D68" s="12" t="n">
-        <v>2548</v>
+        <v>1839</v>
       </c>
       <c r="E68" s="3" t="n"/>
       <c r="F68" s="3" t="n"/>
@@ -8235,17 +7743,17 @@
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>2011-02-04</t>
+          <t>2011-02-10</t>
         </is>
       </c>
       <c r="B69" s="12" t="n">
-        <v>4248</v>
+        <v>3908</v>
       </c>
       <c r="C69" s="12" t="n">
-        <v>4033</v>
+        <v>4749</v>
       </c>
       <c r="D69" s="12" t="n">
-        <v>3027</v>
+        <v>3125</v>
       </c>
       <c r="E69" s="3" t="n"/>
       <c r="F69" s="3" t="n"/>
@@ -8273,17 +7781,17 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>2011-02-05</t>
+          <t>2011-02-11</t>
         </is>
       </c>
       <c r="B70" s="12" t="n">
-        <v>4895</v>
+        <v>5004</v>
       </c>
       <c r="C70" s="12" t="n">
-        <v>2618</v>
+        <v>5075</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>1971</v>
+        <v>3106</v>
       </c>
       <c r="E70" s="3" t="n"/>
       <c r="F70" s="3" t="n"/>
@@ -8311,17 +7819,17 @@
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>2011-02-06</t>
+          <t>2011-02-12</t>
         </is>
       </c>
       <c r="B71" s="12" t="n">
-        <v>3676</v>
+        <v>5292</v>
       </c>
       <c r="C71" s="12" t="n">
-        <v>2775</v>
+        <v>3777</v>
       </c>
       <c r="D71" s="12" t="n">
-        <v>1548</v>
+        <v>2454</v>
       </c>
       <c r="E71" s="3" t="n"/>
       <c r="F71" s="3" t="n"/>
@@ -8349,17 +7857,17 @@
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>2011-02-07</t>
+          <t>2011-02-13</t>
         </is>
       </c>
       <c r="B72" s="12" t="n">
-        <v>4090</v>
+        <v>2135</v>
       </c>
       <c r="C72" s="12" t="n">
-        <v>3239</v>
+        <v>2670</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>1902</v>
+        <v>1739</v>
       </c>
       <c r="E72" s="3" t="n"/>
       <c r="F72" s="3" t="n"/>
@@ -8387,17 +7895,17 @@
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>2011-02-08</t>
+          <t>2011-02-14</t>
         </is>
       </c>
       <c r="B73" s="12" t="n">
-        <v>5170</v>
+        <v>5103</v>
       </c>
       <c r="C73" s="12" t="n">
-        <v>3553</v>
+        <v>2774</v>
       </c>
       <c r="D73" s="12" t="n">
-        <v>2190</v>
+        <v>2219</v>
       </c>
       <c r="E73" s="3" t="n"/>
       <c r="F73" s="3" t="n"/>
@@ -8425,17 +7933,17 @@
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>2011-02-09</t>
+          <t>2011-02-15</t>
         </is>
       </c>
       <c r="B74" s="12" t="n">
-        <v>5365</v>
+        <v>5964</v>
       </c>
       <c r="C74" s="12" t="n">
-        <v>3887</v>
+        <v>5414</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>1839</v>
+        <v>2217</v>
       </c>
       <c r="E74" s="3" t="n"/>
       <c r="F74" s="3" t="n"/>
@@ -8463,17 +7971,17 @@
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>2011-02-10</t>
+          <t>2011-02-16</t>
         </is>
       </c>
       <c r="B75" s="12" t="n">
-        <v>3908</v>
+        <v>5426</v>
       </c>
       <c r="C75" s="12" t="n">
-        <v>4749</v>
+        <v>8266</v>
       </c>
       <c r="D75" s="12" t="n">
-        <v>3125</v>
+        <v>3102</v>
       </c>
       <c r="E75" s="3" t="n"/>
       <c r="F75" s="3" t="n"/>
@@ -8501,17 +8009,17 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>2011-02-11</t>
+          <t>2011-02-17</t>
         </is>
       </c>
       <c r="B76" s="12" t="n">
-        <v>5004</v>
+        <v>4435</v>
       </c>
       <c r="C76" s="12" t="n">
-        <v>5075</v>
+        <v>3541</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>3106</v>
+        <v>3122</v>
       </c>
       <c r="E76" s="3" t="n"/>
       <c r="F76" s="3" t="n"/>
@@ -8539,17 +8047,17 @@
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>2011-02-12</t>
+          <t>2011-02-18</t>
         </is>
       </c>
       <c r="B77" s="12" t="n">
-        <v>5292</v>
+        <v>5316</v>
       </c>
       <c r="C77" s="12" t="n">
-        <v>3777</v>
+        <v>4062</v>
       </c>
       <c r="D77" s="12" t="n">
-        <v>2454</v>
+        <v>1991</v>
       </c>
       <c r="E77" s="3" t="n"/>
       <c r="F77" s="3" t="n"/>
@@ -8577,17 +8085,17 @@
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>2011-02-13</t>
+          <t>2011-02-19</t>
         </is>
       </c>
       <c r="B78" s="12" t="n">
-        <v>2135</v>
+        <v>3877</v>
       </c>
       <c r="C78" s="12" t="n">
-        <v>2670</v>
+        <v>3708</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>1739</v>
+        <v>1953</v>
       </c>
       <c r="E78" s="3" t="n"/>
       <c r="F78" s="3" t="n"/>
@@ -8615,17 +8123,17 @@
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>2011-02-14</t>
+          <t>2011-02-20</t>
         </is>
       </c>
       <c r="B79" s="12" t="n">
-        <v>5103</v>
+        <v>2974</v>
       </c>
       <c r="C79" s="12" t="n">
-        <v>2774</v>
+        <v>3418</v>
       </c>
       <c r="D79" s="12" t="n">
-        <v>2219</v>
+        <v>1356</v>
       </c>
       <c r="E79" s="3" t="n"/>
       <c r="F79" s="3" t="n"/>
@@ -8653,17 +8161,17 @@
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>2011-02-15</t>
+          <t>2011-02-21</t>
         </is>
       </c>
       <c r="B80" s="12" t="n">
-        <v>5964</v>
+        <v>3962</v>
       </c>
       <c r="C80" s="12" t="n">
-        <v>5414</v>
+        <v>3018</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>2217</v>
+        <v>1888</v>
       </c>
       <c r="E80" s="3" t="n"/>
       <c r="F80" s="3" t="n"/>
@@ -8691,17 +8199,17 @@
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>2011-02-16</t>
+          <t>2011-02-22</t>
         </is>
       </c>
       <c r="B81" s="12" t="n">
-        <v>5426</v>
+        <v>4485</v>
       </c>
       <c r="C81" s="12" t="n">
-        <v>8266</v>
+        <v>3967</v>
       </c>
       <c r="D81" s="12" t="n">
-        <v>3102</v>
+        <v>2107</v>
       </c>
       <c r="E81" s="3" t="n"/>
       <c r="F81" s="3" t="n"/>
@@ -8729,17 +8237,17 @@
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>2011-02-17</t>
+          <t>2011-02-23</t>
         </is>
       </c>
       <c r="B82" s="12" t="n">
-        <v>4435</v>
+        <v>4161</v>
       </c>
       <c r="C82" s="12" t="n">
-        <v>3541</v>
+        <v>3268</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>3122</v>
+        <v>2496</v>
       </c>
       <c r="E82" s="3" t="n"/>
       <c r="F82" s="3" t="n"/>
@@ -8767,17 +8275,17 @@
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>2011-02-18</t>
+          <t>2011-02-24</t>
         </is>
       </c>
       <c r="B83" s="12" t="n">
-        <v>5316</v>
+        <v>2150</v>
       </c>
       <c r="C83" s="12" t="n">
-        <v>4062</v>
+        <v>2114</v>
       </c>
       <c r="D83" s="12" t="n">
-        <v>1991</v>
+        <v>1981</v>
       </c>
       <c r="E83" s="3" t="n"/>
       <c r="F83" s="3" t="n"/>
@@ -8805,17 +8313,17 @@
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>2011-02-19</t>
+          <t>2011-02-25</t>
         </is>
       </c>
       <c r="B84" s="12" t="n">
-        <v>3877</v>
+        <v>1683</v>
       </c>
       <c r="C84" s="12" t="n">
-        <v>3708</v>
+        <v>2456</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>1953</v>
+        <v>1875</v>
       </c>
       <c r="E84" s="3" t="n"/>
       <c r="F84" s="3" t="n"/>
@@ -8843,17 +8351,17 @@
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>2011-02-20</t>
+          <t>2011-02-26</t>
         </is>
       </c>
       <c r="B85" s="12" t="n">
-        <v>2974</v>
+        <v>1522</v>
       </c>
       <c r="C85" s="12" t="n">
-        <v>3418</v>
+        <v>2072</v>
       </c>
       <c r="D85" s="12" t="n">
-        <v>1356</v>
+        <v>1603</v>
       </c>
       <c r="E85" s="3" t="n"/>
       <c r="F85" s="3" t="n"/>
@@ -8881,17 +8389,17 @@
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>2011-02-21</t>
+          <t>2011-02-27</t>
         </is>
       </c>
       <c r="B86" s="12" t="n">
-        <v>3962</v>
+        <v>1531</v>
       </c>
       <c r="C86" s="12" t="n">
-        <v>3018</v>
+        <v>1154</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>1888</v>
+        <v>3788</v>
       </c>
       <c r="E86" s="3" t="n"/>
       <c r="F86" s="3" t="n"/>
@@ -8919,17 +8427,17 @@
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>2011-02-22</t>
+          <t>2011-02-28</t>
         </is>
       </c>
       <c r="B87" s="12" t="n">
-        <v>4485</v>
+        <v>3194</v>
       </c>
       <c r="C87" s="12" t="n">
-        <v>3967</v>
+        <v>3494</v>
       </c>
       <c r="D87" s="12" t="n">
-        <v>2107</v>
+        <v>2362</v>
       </c>
       <c r="E87" s="3" t="n"/>
       <c r="F87" s="3" t="n"/>
@@ -8957,17 +8465,17 @@
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>2011-02-23</t>
+          <t>2011-03-01</t>
         </is>
       </c>
       <c r="B88" s="12" t="n">
-        <v>4161</v>
+        <v>2249</v>
       </c>
       <c r="C88" s="12" t="n">
-        <v>3268</v>
+        <v>1488</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>2496</v>
+        <v>1894</v>
       </c>
       <c r="E88" s="3" t="n"/>
       <c r="F88" s="3" t="n"/>
@@ -8995,17 +8503,17 @@
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>2011-02-24</t>
+          <t>2011-03-02</t>
         </is>
       </c>
       <c r="B89" s="12" t="n">
-        <v>2150</v>
+        <v>2599</v>
       </c>
       <c r="C89" s="12" t="n">
-        <v>2114</v>
+        <v>1667</v>
       </c>
       <c r="D89" s="12" t="n">
-        <v>1981</v>
+        <v>2014</v>
       </c>
       <c r="E89" s="3" t="n"/>
       <c r="F89" s="3" t="n"/>
@@ -9033,17 +8541,17 @@
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>2011-02-25</t>
+          <t>2011-03-03</t>
         </is>
       </c>
       <c r="B90" s="12" t="n">
-        <v>1683</v>
+        <v>2028</v>
       </c>
       <c r="C90" s="12" t="n">
-        <v>2456</v>
+        <v>1789</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>1875</v>
+        <v>2840</v>
       </c>
       <c r="E90" s="3" t="n"/>
       <c r="F90" s="3" t="n"/>
@@ -9071,17 +8579,17 @@
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>2011-02-26</t>
+          <t>2011-03-04</t>
         </is>
       </c>
       <c r="B91" s="12" t="n">
-        <v>1522</v>
+        <v>1494</v>
       </c>
       <c r="C91" s="12" t="n">
-        <v>2072</v>
+        <v>1581</v>
       </c>
       <c r="D91" s="12" t="n">
-        <v>1603</v>
+        <v>2497</v>
       </c>
       <c r="E91" s="3" t="n"/>
       <c r="F91" s="3" t="n"/>
@@ -9109,17 +8617,17 @@
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>2011-02-27</t>
+          <t>2011-03-05</t>
         </is>
       </c>
       <c r="B92" s="12" t="n">
-        <v>1531</v>
+        <v>2248</v>
       </c>
       <c r="C92" s="12" t="n">
-        <v>1154</v>
+        <v>1754</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>3788</v>
+        <v>2430</v>
       </c>
       <c r="E92" s="3" t="n"/>
       <c r="F92" s="3" t="n"/>
@@ -9147,17 +8655,17 @@
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>2011-02-28</t>
+          <t>2011-03-06</t>
         </is>
       </c>
       <c r="B93" s="12" t="n">
-        <v>3194</v>
+        <v>2087</v>
       </c>
       <c r="C93" s="12" t="n">
-        <v>3494</v>
+        <v>2099</v>
       </c>
       <c r="D93" s="12" t="n">
-        <v>2362</v>
+        <v>1391</v>
       </c>
       <c r="E93" s="3" t="n"/>
       <c r="F93" s="3" t="n"/>
@@ -9185,17 +8693,17 @@
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>2011-03-01</t>
+          <t>2011-03-07</t>
         </is>
       </c>
       <c r="B94" s="12" t="n">
-        <v>2249</v>
+        <v>1491</v>
       </c>
       <c r="C94" s="12" t="n">
-        <v>1488</v>
+        <v>1790</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>1894</v>
+        <v>1662</v>
       </c>
       <c r="E94" s="3" t="n"/>
       <c r="F94" s="3" t="n"/>
@@ -9223,17 +8731,17 @@
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>2011-03-02</t>
+          <t>2011-03-08</t>
         </is>
       </c>
       <c r="B95" s="12" t="n">
-        <v>2599</v>
+        <v>1725</v>
       </c>
       <c r="C95" s="12" t="n">
-        <v>1667</v>
+        <v>2144</v>
       </c>
       <c r="D95" s="12" t="n">
-        <v>2014</v>
+        <v>2381</v>
       </c>
       <c r="E95" s="3" t="n"/>
       <c r="F95" s="3" t="n"/>
@@ -9261,17 +8769,17 @@
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>2011-03-03</t>
+          <t>2011-03-09</t>
         </is>
       </c>
       <c r="B96" s="12" t="n">
-        <v>2028</v>
+        <v>2777</v>
       </c>
       <c r="C96" s="12" t="n">
-        <v>1789</v>
+        <v>1987</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>2840</v>
+        <v>2472</v>
       </c>
       <c r="E96" s="3" t="n"/>
       <c r="F96" s="3" t="n"/>
@@ -9299,17 +8807,17 @@
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>2011-03-04</t>
+          <t>2011-03-10</t>
         </is>
       </c>
       <c r="B97" s="12" t="n">
-        <v>1494</v>
+        <v>3387</v>
       </c>
       <c r="C97" s="12" t="n">
-        <v>1581</v>
+        <v>2884</v>
       </c>
       <c r="D97" s="12" t="n">
-        <v>2497</v>
+        <v>3845</v>
       </c>
       <c r="E97" s="3" t="n"/>
       <c r="F97" s="3" t="n"/>
@@ -9337,17 +8845,17 @@
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>2011-03-05</t>
+          <t>2011-03-11</t>
         </is>
       </c>
       <c r="B98" s="12" t="n">
-        <v>2248</v>
+        <v>6379</v>
       </c>
       <c r="C98" s="12" t="n">
-        <v>1754</v>
+        <v>6439</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>2430</v>
+        <v>8300</v>
       </c>
       <c r="E98" s="3" t="n"/>
       <c r="F98" s="3" t="n"/>
@@ -9375,17 +8883,17 @@
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>2011-03-06</t>
+          <t>2011-03-12</t>
         </is>
       </c>
       <c r="B99" s="12" t="n">
-        <v>2087</v>
+        <v>6737</v>
       </c>
       <c r="C99" s="12" t="n">
-        <v>2099</v>
+        <v>8478</v>
       </c>
       <c r="D99" s="12" t="n">
-        <v>1391</v>
+        <v>6946</v>
       </c>
       <c r="E99" s="3" t="n"/>
       <c r="F99" s="3" t="n"/>
@@ -9413,17 +8921,17 @@
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>2011-03-07</t>
+          <t>2011-03-13</t>
         </is>
       </c>
       <c r="B100" s="12" t="n">
-        <v>1491</v>
+        <v>5138</v>
       </c>
       <c r="C100" s="12" t="n">
-        <v>1790</v>
+        <v>5582</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1662</v>
+        <v>5773</v>
       </c>
       <c r="E100" s="3" t="n"/>
       <c r="F100" s="3" t="n"/>
@@ -9451,17 +8959,17 @@
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>2011-03-08</t>
+          <t>2011-03-14</t>
         </is>
       </c>
       <c r="B101" s="12" t="n">
-        <v>1725</v>
+        <v>8159</v>
       </c>
       <c r="C101" s="12" t="n">
-        <v>2144</v>
+        <v>6007</v>
       </c>
       <c r="D101" s="12" t="n">
-        <v>2381</v>
+        <v>5528</v>
       </c>
       <c r="E101" s="3" t="n"/>
       <c r="F101" s="3" t="n"/>
@@ -9489,17 +8997,17 @@
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>2011-03-09</t>
+          <t>2011-03-15</t>
         </is>
       </c>
       <c r="B102" s="12" t="n">
-        <v>2777</v>
+        <v>4154</v>
       </c>
       <c r="C102" s="12" t="n">
-        <v>1987</v>
+        <v>3160</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>2472</v>
+        <v>4566</v>
       </c>
       <c r="E102" s="3" t="n"/>
       <c r="F102" s="3" t="n"/>
@@ -9527,17 +9035,17 @@
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>2011-03-10</t>
+          <t>2011-03-16</t>
         </is>
       </c>
       <c r="B103" s="12" t="n">
-        <v>3387</v>
+        <v>3812</v>
       </c>
       <c r="C103" s="12" t="n">
-        <v>2884</v>
+        <v>3497</v>
       </c>
       <c r="D103" s="12" t="n">
-        <v>3845</v>
+        <v>3540</v>
       </c>
       <c r="E103" s="3" t="n"/>
       <c r="F103" s="3" t="n"/>
@@ -9565,17 +9073,17 @@
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>2011-03-11</t>
+          <t>2011-03-17</t>
         </is>
       </c>
       <c r="B104" s="12" t="n">
-        <v>6379</v>
+        <v>1995</v>
       </c>
       <c r="C104" s="12" t="n">
-        <v>6439</v>
+        <v>2537</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>8300</v>
+        <v>3144</v>
       </c>
       <c r="E104" s="3" t="n"/>
       <c r="F104" s="3" t="n"/>
@@ -9603,17 +9111,17 @@
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>2011-03-12</t>
+          <t>2011-03-18</t>
         </is>
       </c>
       <c r="B105" s="12" t="n">
-        <v>6737</v>
+        <v>2701</v>
       </c>
       <c r="C105" s="12" t="n">
-        <v>8478</v>
+        <v>3274</v>
       </c>
       <c r="D105" s="12" t="n">
-        <v>6946</v>
+        <v>3217</v>
       </c>
       <c r="E105" s="3" t="n"/>
       <c r="F105" s="3" t="n"/>
@@ -9641,17 +9149,17 @@
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>2011-03-13</t>
+          <t>2011-03-19</t>
         </is>
       </c>
       <c r="B106" s="12" t="n">
-        <v>5138</v>
+        <v>2692</v>
       </c>
       <c r="C106" s="12" t="n">
-        <v>5582</v>
+        <v>3488</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>5773</v>
+        <v>2323</v>
       </c>
       <c r="E106" s="3" t="n"/>
       <c r="F106" s="3" t="n"/>
@@ -9679,17 +9187,17 @@
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>2011-03-14</t>
+          <t>2011-03-20</t>
         </is>
       </c>
       <c r="B107" s="12" t="n">
-        <v>8159</v>
+        <v>1887</v>
       </c>
       <c r="C107" s="12" t="n">
-        <v>6007</v>
+        <v>2635</v>
       </c>
       <c r="D107" s="12" t="n">
-        <v>5528</v>
+        <v>1968</v>
       </c>
       <c r="E107" s="3" t="n"/>
       <c r="F107" s="3" t="n"/>
@@ -9717,17 +9225,17 @@
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>2011-03-15</t>
+          <t>2011-03-21</t>
         </is>
       </c>
       <c r="B108" s="12" t="n">
-        <v>4154</v>
+        <v>1803</v>
       </c>
       <c r="C108" s="12" t="n">
-        <v>3160</v>
+        <v>1965</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>4566</v>
+        <v>3515</v>
       </c>
       <c r="E108" s="3" t="n"/>
       <c r="F108" s="3" t="n"/>
@@ -9755,17 +9263,17 @@
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>2011-03-16</t>
+          <t>2011-03-22</t>
         </is>
       </c>
       <c r="B109" s="12" t="n">
-        <v>3812</v>
+        <v>3665</v>
       </c>
       <c r="C109" s="12" t="n">
-        <v>3497</v>
+        <v>2876</v>
       </c>
       <c r="D109" s="12" t="n">
-        <v>3540</v>
+        <v>2679</v>
       </c>
       <c r="E109" s="3" t="n"/>
       <c r="F109" s="3" t="n"/>
@@ -9793,17 +9301,17 @@
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>2011-03-17</t>
+          <t>2011-03-23</t>
         </is>
       </c>
       <c r="B110" s="12" t="n">
-        <v>1995</v>
+        <v>2835</v>
       </c>
       <c r="C110" s="12" t="n">
-        <v>2537</v>
+        <v>3373</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>3144</v>
+        <v>3339</v>
       </c>
       <c r="E110" s="3" t="n"/>
       <c r="F110" s="3" t="n"/>
@@ -9831,17 +9339,17 @@
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>2011-03-18</t>
+          <t>2011-03-24</t>
         </is>
       </c>
       <c r="B111" s="12" t="n">
-        <v>2701</v>
+        <v>3780</v>
       </c>
       <c r="C111" s="12" t="n">
-        <v>3274</v>
+        <v>3389</v>
       </c>
       <c r="D111" s="12" t="n">
-        <v>3217</v>
+        <v>3367</v>
       </c>
       <c r="E111" s="3" t="n"/>
       <c r="F111" s="3" t="n"/>
@@ -9869,17 +9377,17 @@
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>2011-03-19</t>
+          <t>2011-03-25</t>
         </is>
       </c>
       <c r="B112" s="12" t="n">
-        <v>2692</v>
+        <v>3893</v>
       </c>
       <c r="C112" s="12" t="n">
-        <v>3488</v>
+        <v>1844</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>2323</v>
+        <v>2339</v>
       </c>
       <c r="E112" s="3" t="n"/>
       <c r="F112" s="3" t="n"/>
@@ -9907,17 +9415,17 @@
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>2011-03-20</t>
+          <t>2011-03-26</t>
         </is>
       </c>
       <c r="B113" s="12" t="n">
-        <v>1887</v>
+        <v>2067</v>
       </c>
       <c r="C113" s="12" t="n">
-        <v>2635</v>
+        <v>2585</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>1968</v>
+        <v>2373</v>
       </c>
       <c r="E113" s="3" t="n"/>
       <c r="F113" s="3" t="n"/>
@@ -9945,17 +9453,17 @@
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>2011-03-21</t>
+          <t>2011-03-27</t>
         </is>
       </c>
       <c r="B114" s="12" t="n">
-        <v>1803</v>
+        <v>1504</v>
       </c>
       <c r="C114" s="12" t="n">
-        <v>1965</v>
+        <v>1131</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>3515</v>
+        <v>1853</v>
       </c>
       <c r="E114" s="3" t="n"/>
       <c r="F114" s="3" t="n"/>
@@ -9983,17 +9491,17 @@
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>2011-03-22</t>
+          <t>2011-03-28</t>
         </is>
       </c>
       <c r="B115" s="12" t="n">
-        <v>3665</v>
+        <v>1233</v>
       </c>
       <c r="C115" s="12" t="n">
-        <v>2876</v>
+        <v>1994</v>
       </c>
       <c r="D115" s="12" t="n">
-        <v>2679</v>
+        <v>1684</v>
       </c>
       <c r="E115" s="3" t="n"/>
       <c r="F115" s="3" t="n"/>
@@ -10021,17 +9529,17 @@
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>2011-03-23</t>
+          <t>2011-03-29</t>
         </is>
       </c>
       <c r="B116" s="12" t="n">
-        <v>2835</v>
+        <v>2901</v>
       </c>
       <c r="C116" s="12" t="n">
-        <v>3373</v>
+        <v>2339</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>3339</v>
+        <v>2056</v>
       </c>
       <c r="E116" s="3" t="n"/>
       <c r="F116" s="3" t="n"/>
@@ -10059,17 +9567,17 @@
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>2011-03-24</t>
+          <t>2011-03-30</t>
         </is>
       </c>
       <c r="B117" s="12" t="n">
-        <v>3780</v>
+        <v>3430</v>
       </c>
       <c r="C117" s="12" t="n">
-        <v>3389</v>
+        <v>3093</v>
       </c>
       <c r="D117" s="12" t="n">
-        <v>3367</v>
+        <v>2530</v>
       </c>
       <c r="E117" s="3" t="n"/>
       <c r="F117" s="3" t="n"/>
@@ -10097,17 +9605,17 @@
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>2011-03-25</t>
+          <t>2011-03-31</t>
         </is>
       </c>
       <c r="B118" s="12" t="n">
-        <v>3893</v>
+        <v>2202</v>
       </c>
       <c r="C118" s="12" t="n">
-        <v>1844</v>
+        <v>2858</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>2339</v>
+        <v>3170</v>
       </c>
       <c r="E118" s="3" t="n"/>
       <c r="F118" s="3" t="n"/>
@@ -10135,17 +9643,17 @@
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>2011-03-26</t>
+          <t>2011-04-01</t>
         </is>
       </c>
       <c r="B119" s="12" t="n">
-        <v>2067</v>
+        <v>4191</v>
       </c>
       <c r="C119" s="12" t="n">
-        <v>2585</v>
+        <v>2879</v>
       </c>
       <c r="D119" s="12" t="n">
-        <v>2373</v>
+        <v>3036</v>
       </c>
       <c r="E119" s="3" t="n"/>
       <c r="F119" s="3" t="n"/>
@@ -10173,17 +9681,17 @@
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>2011-03-27</t>
+          <t>2011-04-02</t>
         </is>
       </c>
       <c r="B120" s="12" t="n">
-        <v>1504</v>
+        <v>3957</v>
       </c>
       <c r="C120" s="12" t="n">
-        <v>1131</v>
+        <v>2495</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>1853</v>
+        <v>2106</v>
       </c>
       <c r="E120" s="3" t="n"/>
       <c r="F120" s="3" t="n"/>
@@ -10207,102 +9715,6 @@
       <c r="X120" s="3" t="n"/>
       <c r="Y120" s="3" t="n"/>
       <c r="Z120" s="3" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="11" t="inlineStr">
-        <is>
-          <t>2011-03-28</t>
-        </is>
-      </c>
-      <c r="B121" s="12" t="n">
-        <v>1233</v>
-      </c>
-      <c r="C121" s="12" t="n">
-        <v>1994</v>
-      </c>
-      <c r="D121" s="12" t="n">
-        <v>1684</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="11" t="inlineStr">
-        <is>
-          <t>2011-03-29</t>
-        </is>
-      </c>
-      <c r="B122" s="12" t="n">
-        <v>2901</v>
-      </c>
-      <c r="C122" s="12" t="n">
-        <v>2339</v>
-      </c>
-      <c r="D122" s="12" t="n">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="11" t="inlineStr">
-        <is>
-          <t>2011-03-30</t>
-        </is>
-      </c>
-      <c r="B123" s="12" t="n">
-        <v>3430</v>
-      </c>
-      <c r="C123" s="12" t="n">
-        <v>3093</v>
-      </c>
-      <c r="D123" s="12" t="n">
-        <v>2530</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="11" t="inlineStr">
-        <is>
-          <t>2011-03-31</t>
-        </is>
-      </c>
-      <c r="B124" s="12" t="n">
-        <v>2202</v>
-      </c>
-      <c r="C124" s="12" t="n">
-        <v>2858</v>
-      </c>
-      <c r="D124" s="12" t="n">
-        <v>3170</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="11" t="inlineStr">
-        <is>
-          <t>2011-04-01</t>
-        </is>
-      </c>
-      <c r="B125" s="12" t="n">
-        <v>4191</v>
-      </c>
-      <c r="C125" s="12" t="n">
-        <v>2879</v>
-      </c>
-      <c r="D125" s="12" t="n">
-        <v>3036</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="11" t="inlineStr">
-        <is>
-          <t>2011-04-02</t>
-        </is>
-      </c>
-      <c r="B126" s="12" t="n">
-        <v>3957</v>
-      </c>
-      <c r="C126" s="12" t="n">
-        <v>2495</v>
-      </c>
-      <c r="D126" s="12" t="n">
-        <v>2106</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -11202,7 +10614,11 @@
       <c r="Z26" s="3" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="3" t="n"/>
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>Dados diarios para auditoria</t>
+        </is>
+      </c>
       <c r="B27" s="3" t="n"/>
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="n"/>
@@ -11230,10 +10646,26 @@
       <c r="Z27" s="3" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="3" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="n"/>
       <c r="G28" s="3" t="n"/>
@@ -11258,10 +10690,20 @@
       <c r="Z28" s="3" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="3" t="n"/>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>2011-05-01</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="n">
+        <v>2654</v>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>1737</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>497</v>
+      </c>
       <c r="E29" s="3" t="n"/>
       <c r="F29" s="3" t="n"/>
       <c r="G29" s="3" t="n"/>
@@ -11286,10 +10728,20 @@
       <c r="Z29" s="3" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="3" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>2011-05-02</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="n">
+        <v>3723</v>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>1596</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>687</v>
+      </c>
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="n"/>
       <c r="G30" s="3" t="n"/>
@@ -11314,10 +10766,20 @@
       <c r="Z30" s="3" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="3" t="n"/>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>2011-05-03</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="n">
+        <v>5651</v>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>2041</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>832</v>
+      </c>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n"/>
       <c r="G31" s="3" t="n"/>
@@ -11342,10 +10804,20 @@
       <c r="Z31" s="3" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="3" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>2011-05-04</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n">
+        <v>4953</v>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>3269</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>870</v>
+      </c>
       <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="n"/>
       <c r="G32" s="3" t="n"/>
@@ -11370,14 +10842,20 @@
       <c r="Z32" s="3" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>Dados diarios para auditoria</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>2011-05-05</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="n">
+        <v>4049</v>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>1884</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>706</v>
+      </c>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="n"/>
       <c r="G33" s="3" t="n"/>
@@ -11402,25 +10880,19 @@
       <c r="Z33" s="3" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>Grupo 1</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>Grupo 2</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>Grupo 3</t>
-        </is>
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>2011-05-06</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>4268</v>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>3402</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>1309</v>
       </c>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n"/>
@@ -11448,17 +10920,17 @@
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>2011-05-01</t>
+          <t>2011-05-07</t>
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>2654</v>
+        <v>2209</v>
       </c>
       <c r="C35" s="12" t="n">
-        <v>1737</v>
+        <v>1267</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>497</v>
+        <v>405</v>
       </c>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n"/>
@@ -11486,17 +10958,17 @@
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>2011-05-02</t>
+          <t>2011-05-08</t>
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>3723</v>
+        <v>3335</v>
       </c>
       <c r="C36" s="12" t="n">
-        <v>1596</v>
+        <v>1292</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>687</v>
+        <v>561</v>
       </c>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="n"/>
@@ -11524,17 +10996,17 @@
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>2011-05-03</t>
+          <t>2011-05-09</t>
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>5651</v>
+        <v>4185</v>
       </c>
       <c r="C37" s="12" t="n">
-        <v>2041</v>
+        <v>2235</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>832</v>
+        <v>1138</v>
       </c>
       <c r="E37" s="3" t="n"/>
       <c r="F37" s="3" t="n"/>
@@ -11562,17 +11034,17 @@
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>2011-05-04</t>
+          <t>2011-05-10</t>
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>4953</v>
+        <v>4382</v>
       </c>
       <c r="C38" s="12" t="n">
-        <v>3269</v>
+        <v>2334</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>870</v>
+        <v>674</v>
       </c>
       <c r="E38" s="3" t="n"/>
       <c r="F38" s="3" t="n"/>
@@ -11600,17 +11072,17 @@
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>2011-05-05</t>
+          <t>2011-05-11</t>
         </is>
       </c>
       <c r="B39" s="12" t="n">
-        <v>4049</v>
+        <v>6168</v>
       </c>
       <c r="C39" s="12" t="n">
-        <v>1884</v>
+        <v>2449</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>706</v>
+        <v>1102</v>
       </c>
       <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="n"/>
@@ -11638,17 +11110,17 @@
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>2011-05-06</t>
+          <t>2011-05-12</t>
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>4268</v>
+        <v>4112</v>
       </c>
       <c r="C40" s="12" t="n">
-        <v>3402</v>
+        <v>2162</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>1309</v>
+        <v>1155</v>
       </c>
       <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="n"/>
@@ -11676,17 +11148,17 @@
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>2011-05-07</t>
+          <t>2011-05-13</t>
         </is>
       </c>
       <c r="B41" s="12" t="n">
-        <v>2209</v>
+        <v>5681</v>
       </c>
       <c r="C41" s="12" t="n">
-        <v>1267</v>
+        <v>2697</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>405</v>
+        <v>760</v>
       </c>
       <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="n"/>
@@ -11714,17 +11186,17 @@
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>2011-05-08</t>
+          <t>2011-05-14</t>
         </is>
       </c>
       <c r="B42" s="12" t="n">
-        <v>3335</v>
+        <v>2198</v>
       </c>
       <c r="C42" s="12" t="n">
-        <v>1292</v>
+        <v>1274</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>561</v>
+        <v>622</v>
       </c>
       <c r="E42" s="3" t="n"/>
       <c r="F42" s="3" t="n"/>
@@ -11752,17 +11224,17 @@
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>2011-05-09</t>
+          <t>2011-05-15</t>
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>4185</v>
+        <v>15012</v>
       </c>
       <c r="C43" s="12" t="n">
-        <v>2235</v>
+        <v>7965</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>1138</v>
+        <v>2763</v>
       </c>
       <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="n"/>
@@ -11790,17 +11262,17 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>2011-05-10</t>
+          <t>2011-05-16</t>
         </is>
       </c>
       <c r="B44" s="12" t="n">
-        <v>4382</v>
+        <v>5922</v>
       </c>
       <c r="C44" s="12" t="n">
-        <v>2334</v>
+        <v>2252</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>674</v>
+        <v>572</v>
       </c>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
@@ -11828,17 +11300,17 @@
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>2011-05-11</t>
+          <t>2011-05-17</t>
         </is>
       </c>
       <c r="B45" s="12" t="n">
-        <v>6168</v>
+        <v>5714</v>
       </c>
       <c r="C45" s="12" t="n">
-        <v>2449</v>
+        <v>1666</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>1102</v>
+        <v>680</v>
       </c>
       <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="n"/>
@@ -11866,17 +11338,17 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>2011-05-12</t>
+          <t>2011-05-18</t>
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>4112</v>
+        <v>4756</v>
       </c>
       <c r="C46" s="12" t="n">
-        <v>2162</v>
+        <v>2315</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>1155</v>
+        <v>802</v>
       </c>
       <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="n"/>
@@ -11904,17 +11376,17 @@
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>2011-05-13</t>
+          <t>2011-05-19</t>
         </is>
       </c>
       <c r="B47" s="12" t="n">
-        <v>5681</v>
+        <v>6329</v>
       </c>
       <c r="C47" s="12" t="n">
-        <v>2697</v>
+        <v>1940</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>760</v>
+        <v>898</v>
       </c>
       <c r="E47" s="3" t="n"/>
       <c r="F47" s="3" t="n"/>
@@ -11942,17 +11414,17 @@
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>2011-05-14</t>
+          <t>2011-05-20</t>
         </is>
       </c>
       <c r="B48" s="12" t="n">
-        <v>2198</v>
+        <v>6042</v>
       </c>
       <c r="C48" s="12" t="n">
-        <v>1274</v>
+        <v>1998</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>622</v>
+        <v>848</v>
       </c>
       <c r="E48" s="3" t="n"/>
       <c r="F48" s="3" t="n"/>
@@ -11980,17 +11452,17 @@
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>2011-05-15</t>
+          <t>2011-05-21</t>
         </is>
       </c>
       <c r="B49" s="12" t="n">
-        <v>15012</v>
+        <v>2979</v>
       </c>
       <c r="C49" s="12" t="n">
-        <v>7965</v>
+        <v>1632</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>2763</v>
+        <v>677</v>
       </c>
       <c r="E49" s="3" t="n"/>
       <c r="F49" s="3" t="n"/>
@@ -12018,17 +11490,17 @@
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>2011-05-16</t>
+          <t>2011-05-22</t>
         </is>
       </c>
       <c r="B50" s="12" t="n">
-        <v>5922</v>
+        <v>9733</v>
       </c>
       <c r="C50" s="12" t="n">
-        <v>2252</v>
+        <v>5880</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>572</v>
+        <v>2133</v>
       </c>
       <c r="E50" s="3" t="n"/>
       <c r="F50" s="3" t="n"/>
@@ -12056,17 +11528,17 @@
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>2011-05-17</t>
+          <t>2011-05-23</t>
         </is>
       </c>
       <c r="B51" s="12" t="n">
-        <v>5714</v>
+        <v>3316</v>
       </c>
       <c r="C51" s="12" t="n">
-        <v>1666</v>
+        <v>2137</v>
       </c>
       <c r="D51" s="12" t="n">
-        <v>680</v>
+        <v>729</v>
       </c>
       <c r="E51" s="3" t="n"/>
       <c r="F51" s="3" t="n"/>
@@ -12094,17 +11566,17 @@
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>2011-05-18</t>
+          <t>2011-05-24</t>
         </is>
       </c>
       <c r="B52" s="12" t="n">
-        <v>4756</v>
+        <v>3449</v>
       </c>
       <c r="C52" s="12" t="n">
-        <v>2315</v>
+        <v>1686</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>802</v>
+        <v>691</v>
       </c>
       <c r="E52" s="3" t="n"/>
       <c r="F52" s="3" t="n"/>
@@ -12132,17 +11604,17 @@
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>2011-05-19</t>
+          <t>2011-05-25</t>
         </is>
       </c>
       <c r="B53" s="12" t="n">
-        <v>6329</v>
+        <v>4993</v>
       </c>
       <c r="C53" s="12" t="n">
-        <v>1940</v>
+        <v>3048</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>898</v>
+        <v>847</v>
       </c>
       <c r="E53" s="3" t="n"/>
       <c r="F53" s="3" t="n"/>
@@ -12170,17 +11642,17 @@
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>2011-05-20</t>
+          <t>2011-05-26</t>
         </is>
       </c>
       <c r="B54" s="12" t="n">
-        <v>6042</v>
+        <v>4279</v>
       </c>
       <c r="C54" s="12" t="n">
-        <v>1998</v>
+        <v>2780</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>848</v>
+        <v>1051</v>
       </c>
       <c r="E54" s="3" t="n"/>
       <c r="F54" s="3" t="n"/>
@@ -12208,14 +11680,14 @@
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>2011-05-21</t>
+          <t>2011-05-27</t>
         </is>
       </c>
       <c r="B55" s="12" t="n">
-        <v>2979</v>
+        <v>5131</v>
       </c>
       <c r="C55" s="12" t="n">
-        <v>1632</v>
+        <v>2461</v>
       </c>
       <c r="D55" s="12" t="n">
         <v>677</v>
@@ -12246,17 +11718,17 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>2011-05-22</t>
+          <t>2011-05-28</t>
         </is>
       </c>
       <c r="B56" s="12" t="n">
-        <v>9733</v>
+        <v>3685</v>
       </c>
       <c r="C56" s="12" t="n">
-        <v>5880</v>
+        <v>1239</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>2133</v>
+        <v>527</v>
       </c>
       <c r="E56" s="3" t="n"/>
       <c r="F56" s="3" t="n"/>
@@ -12284,17 +11756,17 @@
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>2011-05-23</t>
+          <t>2011-05-29</t>
         </is>
       </c>
       <c r="B57" s="12" t="n">
-        <v>3316</v>
+        <v>2782</v>
       </c>
       <c r="C57" s="12" t="n">
-        <v>2137</v>
+        <v>1412</v>
       </c>
       <c r="D57" s="12" t="n">
-        <v>729</v>
+        <v>656</v>
       </c>
       <c r="E57" s="3" t="n"/>
       <c r="F57" s="3" t="n"/>
@@ -12322,17 +11794,17 @@
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>2011-05-24</t>
+          <t>2011-05-30</t>
         </is>
       </c>
       <c r="B58" s="12" t="n">
-        <v>3449</v>
+        <v>3742</v>
       </c>
       <c r="C58" s="12" t="n">
-        <v>1686</v>
+        <v>2752</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>691</v>
+        <v>999</v>
       </c>
       <c r="E58" s="3" t="n"/>
       <c r="F58" s="3" t="n"/>
@@ -12360,17 +11832,17 @@
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>2011-05-25</t>
+          <t>2011-05-31</t>
         </is>
       </c>
       <c r="B59" s="12" t="n">
-        <v>4993</v>
+        <v>6189</v>
       </c>
       <c r="C59" s="12" t="n">
-        <v>3048</v>
+        <v>2400</v>
       </c>
       <c r="D59" s="12" t="n">
-        <v>847</v>
+        <v>584</v>
       </c>
       <c r="E59" s="3" t="n"/>
       <c r="F59" s="3" t="n"/>
@@ -12398,17 +11870,17 @@
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>2011-05-26</t>
+          <t>2011-06-01</t>
         </is>
       </c>
       <c r="B60" s="12" t="n">
-        <v>4279</v>
+        <v>5472</v>
       </c>
       <c r="C60" s="12" t="n">
-        <v>2780</v>
+        <v>2166</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>1051</v>
+        <v>917</v>
       </c>
       <c r="E60" s="3" t="n"/>
       <c r="F60" s="3" t="n"/>
@@ -12436,17 +11908,17 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>2011-05-27</t>
+          <t>2011-06-02</t>
         </is>
       </c>
       <c r="B61" s="12" t="n">
-        <v>5131</v>
+        <v>6750</v>
       </c>
       <c r="C61" s="12" t="n">
-        <v>2461</v>
+        <v>2690</v>
       </c>
       <c r="D61" s="12" t="n">
-        <v>677</v>
+        <v>1202</v>
       </c>
       <c r="E61" s="3" t="n"/>
       <c r="F61" s="3" t="n"/>
@@ -12474,17 +11946,17 @@
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>2011-05-28</t>
+          <t>2011-06-03</t>
         </is>
       </c>
       <c r="B62" s="12" t="n">
-        <v>3685</v>
+        <v>3491</v>
       </c>
       <c r="C62" s="12" t="n">
-        <v>1239</v>
+        <v>2012</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>527</v>
+        <v>928</v>
       </c>
       <c r="E62" s="3" t="n"/>
       <c r="F62" s="3" t="n"/>
@@ -12512,17 +11984,17 @@
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>2011-05-29</t>
+          <t>2011-06-04</t>
         </is>
       </c>
       <c r="B63" s="12" t="n">
-        <v>2782</v>
+        <v>2708</v>
       </c>
       <c r="C63" s="12" t="n">
-        <v>1412</v>
+        <v>1422</v>
       </c>
       <c r="D63" s="12" t="n">
-        <v>656</v>
+        <v>428</v>
       </c>
       <c r="E63" s="3" t="n"/>
       <c r="F63" s="3" t="n"/>
@@ -12550,17 +12022,17 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>2011-05-30</t>
+          <t>2011-06-05</t>
         </is>
       </c>
       <c r="B64" s="12" t="n">
-        <v>3742</v>
+        <v>3085</v>
       </c>
       <c r="C64" s="12" t="n">
-        <v>2752</v>
+        <v>1520</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>999</v>
+        <v>708</v>
       </c>
       <c r="E64" s="3" t="n"/>
       <c r="F64" s="3" t="n"/>
@@ -12588,17 +12060,17 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>2011-05-31</t>
+          <t>2011-06-06</t>
         </is>
       </c>
       <c r="B65" s="12" t="n">
-        <v>6189</v>
+        <v>5190</v>
       </c>
       <c r="C65" s="12" t="n">
-        <v>2400</v>
+        <v>2559</v>
       </c>
       <c r="D65" s="12" t="n">
-        <v>584</v>
+        <v>829</v>
       </c>
       <c r="E65" s="3" t="n"/>
       <c r="F65" s="3" t="n"/>
@@ -12626,17 +12098,17 @@
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>2011-06-01</t>
+          <t>2011-06-07</t>
         </is>
       </c>
       <c r="B66" s="12" t="n">
-        <v>5472</v>
+        <v>4884</v>
       </c>
       <c r="C66" s="12" t="n">
-        <v>2166</v>
+        <v>1940</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>917</v>
+        <v>804</v>
       </c>
       <c r="E66" s="3" t="n"/>
       <c r="F66" s="3" t="n"/>
@@ -12664,17 +12136,17 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>2011-06-02</t>
+          <t>2011-06-08</t>
         </is>
       </c>
       <c r="B67" s="12" t="n">
-        <v>6750</v>
+        <v>5871</v>
       </c>
       <c r="C67" s="12" t="n">
-        <v>2690</v>
+        <v>3451</v>
       </c>
       <c r="D67" s="12" t="n">
-        <v>1202</v>
+        <v>1225</v>
       </c>
       <c r="E67" s="3" t="n"/>
       <c r="F67" s="3" t="n"/>
@@ -12702,17 +12174,17 @@
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>2011-06-03</t>
+          <t>2011-06-09</t>
         </is>
       </c>
       <c r="B68" s="12" t="n">
-        <v>3491</v>
+        <v>4122</v>
       </c>
       <c r="C68" s="12" t="n">
-        <v>2012</v>
+        <v>3683</v>
       </c>
       <c r="D68" s="12" t="n">
-        <v>928</v>
+        <v>1223</v>
       </c>
       <c r="E68" s="3" t="n"/>
       <c r="F68" s="3" t="n"/>
@@ -12740,17 +12212,17 @@
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>2011-06-04</t>
+          <t>2011-06-10</t>
         </is>
       </c>
       <c r="B69" s="12" t="n">
-        <v>2708</v>
+        <v>4612</v>
       </c>
       <c r="C69" s="12" t="n">
-        <v>1422</v>
+        <v>2478</v>
       </c>
       <c r="D69" s="12" t="n">
-        <v>428</v>
+        <v>728</v>
       </c>
       <c r="E69" s="3" t="n"/>
       <c r="F69" s="3" t="n"/>
@@ -12778,17 +12250,17 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>2011-06-05</t>
+          <t>2011-06-11</t>
         </is>
       </c>
       <c r="B70" s="12" t="n">
-        <v>3085</v>
+        <v>3966</v>
       </c>
       <c r="C70" s="12" t="n">
-        <v>1520</v>
+        <v>1427</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>708</v>
+        <v>622</v>
       </c>
       <c r="E70" s="3" t="n"/>
       <c r="F70" s="3" t="n"/>
@@ -12816,17 +12288,17 @@
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>2011-06-06</t>
+          <t>2011-06-12</t>
         </is>
       </c>
       <c r="B71" s="12" t="n">
-        <v>5190</v>
+        <v>2585</v>
       </c>
       <c r="C71" s="12" t="n">
-        <v>2559</v>
+        <v>1178</v>
       </c>
       <c r="D71" s="12" t="n">
-        <v>829</v>
+        <v>715</v>
       </c>
       <c r="E71" s="3" t="n"/>
       <c r="F71" s="3" t="n"/>
@@ -12854,17 +12326,17 @@
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>2011-06-07</t>
+          <t>2011-06-13</t>
         </is>
       </c>
       <c r="B72" s="12" t="n">
-        <v>4884</v>
+        <v>5920</v>
       </c>
       <c r="C72" s="12" t="n">
-        <v>1940</v>
+        <v>2577</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>804</v>
+        <v>877</v>
       </c>
       <c r="E72" s="3" t="n"/>
       <c r="F72" s="3" t="n"/>
@@ -12892,17 +12364,17 @@
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>2011-06-08</t>
+          <t>2011-06-14</t>
         </is>
       </c>
       <c r="B73" s="12" t="n">
-        <v>5871</v>
+        <v>3070</v>
       </c>
       <c r="C73" s="12" t="n">
-        <v>3451</v>
+        <v>2259</v>
       </c>
       <c r="D73" s="12" t="n">
-        <v>1225</v>
+        <v>806</v>
       </c>
       <c r="E73" s="3" t="n"/>
       <c r="F73" s="3" t="n"/>
@@ -12930,17 +12402,17 @@
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>2011-06-09</t>
+          <t>2011-06-15</t>
         </is>
       </c>
       <c r="B74" s="12" t="n">
-        <v>4122</v>
+        <v>4170</v>
       </c>
       <c r="C74" s="12" t="n">
-        <v>3683</v>
+        <v>2293</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>1223</v>
+        <v>1189</v>
       </c>
       <c r="E74" s="3" t="n"/>
       <c r="F74" s="3" t="n"/>
@@ -12968,17 +12440,17 @@
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>2011-06-10</t>
+          <t>2011-06-16</t>
         </is>
       </c>
       <c r="B75" s="12" t="n">
-        <v>4612</v>
+        <v>5748</v>
       </c>
       <c r="C75" s="12" t="n">
-        <v>2478</v>
+        <v>3738</v>
       </c>
       <c r="D75" s="12" t="n">
-        <v>728</v>
+        <v>891</v>
       </c>
       <c r="E75" s="3" t="n"/>
       <c r="F75" s="3" t="n"/>
@@ -13006,17 +12478,17 @@
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>2011-06-11</t>
+          <t>2011-06-17</t>
         </is>
       </c>
       <c r="B76" s="12" t="n">
-        <v>3966</v>
+        <v>3676</v>
       </c>
       <c r="C76" s="12" t="n">
-        <v>1427</v>
+        <v>2714</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>622</v>
+        <v>786</v>
       </c>
       <c r="E76" s="3" t="n"/>
       <c r="F76" s="3" t="n"/>
@@ -13044,17 +12516,17 @@
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>2011-06-12</t>
+          <t>2011-06-18</t>
         </is>
       </c>
       <c r="B77" s="12" t="n">
-        <v>2585</v>
+        <v>4161</v>
       </c>
       <c r="C77" s="12" t="n">
-        <v>1178</v>
+        <v>1218</v>
       </c>
       <c r="D77" s="12" t="n">
-        <v>715</v>
+        <v>593</v>
       </c>
       <c r="E77" s="3" t="n"/>
       <c r="F77" s="3" t="n"/>
@@ -13082,17 +12554,17 @@
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>2011-06-13</t>
+          <t>2011-06-19</t>
         </is>
       </c>
       <c r="B78" s="12" t="n">
-        <v>5920</v>
+        <v>4332</v>
       </c>
       <c r="C78" s="12" t="n">
-        <v>2577</v>
+        <v>1905</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>877</v>
+        <v>356</v>
       </c>
       <c r="E78" s="3" t="n"/>
       <c r="F78" s="3" t="n"/>
@@ -13120,17 +12592,17 @@
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>2011-06-14</t>
+          <t>2011-06-20</t>
         </is>
       </c>
       <c r="B79" s="12" t="n">
-        <v>3070</v>
+        <v>3883</v>
       </c>
       <c r="C79" s="12" t="n">
-        <v>2259</v>
+        <v>2601</v>
       </c>
       <c r="D79" s="12" t="n">
-        <v>806</v>
+        <v>870</v>
       </c>
       <c r="E79" s="3" t="n"/>
       <c r="F79" s="3" t="n"/>
@@ -13158,17 +12630,17 @@
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>2011-06-15</t>
+          <t>2011-06-21</t>
         </is>
       </c>
       <c r="B80" s="12" t="n">
-        <v>4170</v>
+        <v>5208</v>
       </c>
       <c r="C80" s="12" t="n">
-        <v>2293</v>
+        <v>1855</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>1189</v>
+        <v>938</v>
       </c>
       <c r="E80" s="3" t="n"/>
       <c r="F80" s="3" t="n"/>
@@ -13196,17 +12668,17 @@
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>2011-06-16</t>
+          <t>2011-06-22</t>
         </is>
       </c>
       <c r="B81" s="12" t="n">
-        <v>5748</v>
+        <v>4614</v>
       </c>
       <c r="C81" s="12" t="n">
-        <v>3738</v>
+        <v>2759</v>
       </c>
       <c r="D81" s="12" t="n">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="E81" s="3" t="n"/>
       <c r="F81" s="3" t="n"/>
@@ -13234,17 +12706,17 @@
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>2011-06-17</t>
+          <t>2011-06-23</t>
         </is>
       </c>
       <c r="B82" s="12" t="n">
-        <v>3676</v>
+        <v>4076</v>
       </c>
       <c r="C82" s="12" t="n">
-        <v>2714</v>
+        <v>2494</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>786</v>
+        <v>1150</v>
       </c>
       <c r="E82" s="3" t="n"/>
       <c r="F82" s="3" t="n"/>
@@ -13272,17 +12744,17 @@
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>2011-06-18</t>
+          <t>2011-06-24</t>
         </is>
       </c>
       <c r="B83" s="12" t="n">
-        <v>4161</v>
+        <v>5720</v>
       </c>
       <c r="C83" s="12" t="n">
-        <v>1218</v>
+        <v>1682</v>
       </c>
       <c r="D83" s="12" t="n">
-        <v>593</v>
+        <v>906</v>
       </c>
       <c r="E83" s="3" t="n"/>
       <c r="F83" s="3" t="n"/>
@@ -13310,17 +12782,17 @@
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>2011-06-19</t>
+          <t>2011-06-25</t>
         </is>
       </c>
       <c r="B84" s="12" t="n">
-        <v>4332</v>
+        <v>3559</v>
       </c>
       <c r="C84" s="12" t="n">
-        <v>1905</v>
+        <v>1809</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>356</v>
+        <v>625</v>
       </c>
       <c r="E84" s="3" t="n"/>
       <c r="F84" s="3" t="n"/>
@@ -13348,17 +12820,17 @@
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>2011-06-20</t>
+          <t>2011-06-26</t>
         </is>
       </c>
       <c r="B85" s="12" t="n">
-        <v>3883</v>
+        <v>2664</v>
       </c>
       <c r="C85" s="12" t="n">
-        <v>2601</v>
+        <v>1102</v>
       </c>
       <c r="D85" s="12" t="n">
-        <v>870</v>
+        <v>603</v>
       </c>
       <c r="E85" s="3" t="n"/>
       <c r="F85" s="3" t="n"/>
@@ -13386,17 +12858,17 @@
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>2011-06-21</t>
+          <t>2011-06-27</t>
         </is>
       </c>
       <c r="B86" s="12" t="n">
-        <v>5208</v>
+        <v>6520</v>
       </c>
       <c r="C86" s="12" t="n">
-        <v>1855</v>
+        <v>2477</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>938</v>
+        <v>648</v>
       </c>
       <c r="E86" s="3" t="n"/>
       <c r="F86" s="3" t="n"/>
@@ -13424,17 +12896,17 @@
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>2011-06-22</t>
+          <t>2011-06-28</t>
         </is>
       </c>
       <c r="B87" s="12" t="n">
-        <v>4614</v>
+        <v>4457</v>
       </c>
       <c r="C87" s="12" t="n">
-        <v>2759</v>
+        <v>2534</v>
       </c>
       <c r="D87" s="12" t="n">
-        <v>898</v>
+        <v>856</v>
       </c>
       <c r="E87" s="3" t="n"/>
       <c r="F87" s="3" t="n"/>
@@ -13462,17 +12934,17 @@
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>2011-06-23</t>
+          <t>2011-06-29</t>
         </is>
       </c>
       <c r="B88" s="12" t="n">
-        <v>4076</v>
+        <v>4483</v>
       </c>
       <c r="C88" s="12" t="n">
-        <v>2494</v>
+        <v>2391</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>1150</v>
+        <v>930</v>
       </c>
       <c r="E88" s="3" t="n"/>
       <c r="F88" s="3" t="n"/>
@@ -13500,17 +12972,17 @@
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>2011-06-24</t>
+          <t>2011-06-30</t>
         </is>
       </c>
       <c r="B89" s="12" t="n">
-        <v>5720</v>
+        <v>5952</v>
       </c>
       <c r="C89" s="12" t="n">
-        <v>1682</v>
+        <v>3021</v>
       </c>
       <c r="D89" s="12" t="n">
-        <v>906</v>
+        <v>890</v>
       </c>
       <c r="E89" s="3" t="n"/>
       <c r="F89" s="3" t="n"/>
@@ -13536,20 +13008,10 @@
       <c r="Z89" s="3" t="n"/>
     </row>
     <row r="90" ht="22" customHeight="1">
-      <c r="A90" s="11" t="inlineStr">
-        <is>
-          <t>2011-06-25</t>
-        </is>
-      </c>
-      <c r="B90" s="12" t="n">
-        <v>3559</v>
-      </c>
-      <c r="C90" s="12" t="n">
-        <v>1809</v>
-      </c>
-      <c r="D90" s="12" t="n">
-        <v>625</v>
-      </c>
+      <c r="A90" s="3" t="n"/>
+      <c r="B90" s="3" t="n"/>
+      <c r="C90" s="3" t="n"/>
+      <c r="D90" s="3" t="n"/>
       <c r="E90" s="3" t="n"/>
       <c r="F90" s="3" t="n"/>
       <c r="G90" s="3" t="n"/>
@@ -13574,20 +13036,10 @@
       <c r="Z90" s="3" t="n"/>
     </row>
     <row r="91" ht="22" customHeight="1">
-      <c r="A91" s="11" t="inlineStr">
-        <is>
-          <t>2011-06-26</t>
-        </is>
-      </c>
-      <c r="B91" s="12" t="n">
-        <v>2664</v>
-      </c>
-      <c r="C91" s="12" t="n">
-        <v>1102</v>
-      </c>
-      <c r="D91" s="12" t="n">
-        <v>603</v>
-      </c>
+      <c r="A91" s="3" t="n"/>
+      <c r="B91" s="3" t="n"/>
+      <c r="C91" s="3" t="n"/>
+      <c r="D91" s="3" t="n"/>
       <c r="E91" s="3" t="n"/>
       <c r="F91" s="3" t="n"/>
       <c r="G91" s="3" t="n"/>
@@ -13612,20 +13064,10 @@
       <c r="Z91" s="3" t="n"/>
     </row>
     <row r="92" ht="22" customHeight="1">
-      <c r="A92" s="11" t="inlineStr">
-        <is>
-          <t>2011-06-27</t>
-        </is>
-      </c>
-      <c r="B92" s="12" t="n">
-        <v>6520</v>
-      </c>
-      <c r="C92" s="12" t="n">
-        <v>2477</v>
-      </c>
-      <c r="D92" s="12" t="n">
-        <v>648</v>
-      </c>
+      <c r="A92" s="3" t="n"/>
+      <c r="B92" s="3" t="n"/>
+      <c r="C92" s="3" t="n"/>
+      <c r="D92" s="3" t="n"/>
       <c r="E92" s="3" t="n"/>
       <c r="F92" s="3" t="n"/>
       <c r="G92" s="3" t="n"/>
@@ -13650,20 +13092,10 @@
       <c r="Z92" s="3" t="n"/>
     </row>
     <row r="93" ht="22" customHeight="1">
-      <c r="A93" s="11" t="inlineStr">
-        <is>
-          <t>2011-06-28</t>
-        </is>
-      </c>
-      <c r="B93" s="12" t="n">
-        <v>4457</v>
-      </c>
-      <c r="C93" s="12" t="n">
-        <v>2534</v>
-      </c>
-      <c r="D93" s="12" t="n">
-        <v>856</v>
-      </c>
+      <c r="A93" s="3" t="n"/>
+      <c r="B93" s="3" t="n"/>
+      <c r="C93" s="3" t="n"/>
+      <c r="D93" s="3" t="n"/>
       <c r="E93" s="3" t="n"/>
       <c r="F93" s="3" t="n"/>
       <c r="G93" s="3" t="n"/>
@@ -13688,20 +13120,10 @@
       <c r="Z93" s="3" t="n"/>
     </row>
     <row r="94" ht="22" customHeight="1">
-      <c r="A94" s="11" t="inlineStr">
-        <is>
-          <t>2011-06-29</t>
-        </is>
-      </c>
-      <c r="B94" s="12" t="n">
-        <v>4483</v>
-      </c>
-      <c r="C94" s="12" t="n">
-        <v>2391</v>
-      </c>
-      <c r="D94" s="12" t="n">
-        <v>930</v>
-      </c>
+      <c r="A94" s="3" t="n"/>
+      <c r="B94" s="3" t="n"/>
+      <c r="C94" s="3" t="n"/>
+      <c r="D94" s="3" t="n"/>
       <c r="E94" s="3" t="n"/>
       <c r="F94" s="3" t="n"/>
       <c r="G94" s="3" t="n"/>
@@ -13726,20 +13148,10 @@
       <c r="Z94" s="3" t="n"/>
     </row>
     <row r="95" ht="22" customHeight="1">
-      <c r="A95" s="11" t="inlineStr">
-        <is>
-          <t>2011-06-30</t>
-        </is>
-      </c>
-      <c r="B95" s="12" t="n">
-        <v>5952</v>
-      </c>
-      <c r="C95" s="12" t="n">
-        <v>3021</v>
-      </c>
-      <c r="D95" s="12" t="n">
-        <v>890</v>
-      </c>
+      <c r="A95" s="3" t="n"/>
+      <c r="B95" s="3" t="n"/>
+      <c r="C95" s="3" t="n"/>
+      <c r="D95" s="3" t="n"/>
       <c r="E95" s="3" t="n"/>
       <c r="F95" s="3" t="n"/>
       <c r="G95" s="3" t="n"/>
@@ -15343,7 +14755,11 @@
       <c r="Z26" s="3" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="3" t="n"/>
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>Dados diarios para auditoria</t>
+        </is>
+      </c>
       <c r="B27" s="3" t="n"/>
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="n"/>
@@ -15371,9 +14787,21 @@
       <c r="Z27" s="3" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="3" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
       <c r="D28" s="3" t="n"/>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="n"/>
@@ -15399,9 +14827,17 @@
       <c r="Z28" s="3" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="3" t="n"/>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>2011-07-01</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="n">
+        <v>832</v>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>0</v>
+      </c>
       <c r="D29" s="3" t="n"/>
       <c r="E29" s="3" t="n"/>
       <c r="F29" s="3" t="n"/>
@@ -15427,9 +14863,17 @@
       <c r="Z29" s="3" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="3" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>2011-07-02</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="n">
+        <v>507</v>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>0</v>
+      </c>
       <c r="D30" s="3" t="n"/>
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="n"/>
@@ -15455,9 +14899,17 @@
       <c r="Z30" s="3" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="3" t="n"/>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>2011-07-03</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="n">
+        <v>595</v>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>0</v>
+      </c>
       <c r="D31" s="3" t="n"/>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n"/>
@@ -15483,9 +14935,17 @@
       <c r="Z31" s="3" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="3" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>2011-07-04</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n">
+        <v>998</v>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>0</v>
+      </c>
       <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="n"/>
@@ -15511,13 +14971,17 @@
       <c r="Z32" s="3" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>Dados diarios para auditoria</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>2011-07-05</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="n">
+        <v>642</v>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>0</v>
+      </c>
       <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="n"/>
@@ -15543,20 +15007,16 @@
       <c r="Z33" s="3" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>Grupo 1</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>Grupo 2</t>
-        </is>
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>2011-07-06</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>878</v>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n"/>
@@ -15585,11 +15045,11 @@
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>2011-07-01</t>
+          <t>2011-07-07</t>
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>832</v>
+        <v>944</v>
       </c>
       <c r="C35" s="12" t="n">
         <v>0</v>
@@ -15621,11 +15081,11 @@
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>2011-07-02</t>
+          <t>2011-07-08</t>
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>507</v>
+        <v>895</v>
       </c>
       <c r="C36" s="12" t="n">
         <v>0</v>
@@ -15657,11 +15117,11 @@
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>2011-07-03</t>
+          <t>2011-07-09</t>
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>595</v>
+        <v>505</v>
       </c>
       <c r="C37" s="12" t="n">
         <v>0</v>
@@ -15693,11 +15153,11 @@
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>2011-07-04</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>998</v>
+        <v>475</v>
       </c>
       <c r="C38" s="12" t="n">
         <v>0</v>
@@ -15729,11 +15189,11 @@
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>2011-07-05</t>
+          <t>2011-07-11</t>
         </is>
       </c>
       <c r="B39" s="12" t="n">
-        <v>642</v>
+        <v>655</v>
       </c>
       <c r="C39" s="12" t="n">
         <v>0</v>
@@ -15765,11 +15225,11 @@
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>2011-07-06</t>
+          <t>2011-07-12</t>
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>878</v>
+        <v>1090</v>
       </c>
       <c r="C40" s="12" t="n">
         <v>0</v>
@@ -15801,11 +15261,11 @@
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>2011-07-07</t>
+          <t>2011-07-13</t>
         </is>
       </c>
       <c r="B41" s="12" t="n">
-        <v>944</v>
+        <v>1097</v>
       </c>
       <c r="C41" s="12" t="n">
         <v>0</v>
@@ -15837,11 +15297,11 @@
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>2011-07-08</t>
+          <t>2011-07-14</t>
         </is>
       </c>
       <c r="B42" s="12" t="n">
-        <v>895</v>
+        <v>837</v>
       </c>
       <c r="C42" s="12" t="n">
         <v>0</v>
@@ -15873,11 +15333,11 @@
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>2011-07-09</t>
+          <t>2011-07-15</t>
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>505</v>
+        <v>598</v>
       </c>
       <c r="C43" s="12" t="n">
         <v>0</v>
@@ -15909,11 +15369,11 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
+          <t>2011-07-16</t>
         </is>
       </c>
       <c r="B44" s="12" t="n">
-        <v>475</v>
+        <v>580</v>
       </c>
       <c r="C44" s="12" t="n">
         <v>0</v>
@@ -15945,11 +15405,11 @@
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>2011-07-11</t>
+          <t>2011-07-17</t>
         </is>
       </c>
       <c r="B45" s="12" t="n">
-        <v>655</v>
+        <v>577</v>
       </c>
       <c r="C45" s="12" t="n">
         <v>0</v>
@@ -15981,11 +15441,11 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>2011-07-12</t>
+          <t>2011-07-18</t>
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>1090</v>
+        <v>714</v>
       </c>
       <c r="C46" s="12" t="n">
         <v>0</v>
@@ -16017,11 +15477,11 @@
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>2011-07-13</t>
+          <t>2011-07-19</t>
         </is>
       </c>
       <c r="B47" s="12" t="n">
-        <v>1097</v>
+        <v>953</v>
       </c>
       <c r="C47" s="12" t="n">
         <v>0</v>
@@ -16053,11 +15513,11 @@
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>2011-07-14</t>
+          <t>2011-07-20</t>
         </is>
       </c>
       <c r="B48" s="12" t="n">
-        <v>837</v>
+        <v>870</v>
       </c>
       <c r="C48" s="12" t="n">
         <v>0</v>
@@ -16089,11 +15549,11 @@
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>2011-07-15</t>
+          <t>2011-07-21</t>
         </is>
       </c>
       <c r="B49" s="12" t="n">
-        <v>598</v>
+        <v>727</v>
       </c>
       <c r="C49" s="12" t="n">
         <v>0</v>
@@ -16125,11 +15585,11 @@
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>2011-07-16</t>
+          <t>2011-07-22</t>
         </is>
       </c>
       <c r="B50" s="12" t="n">
-        <v>580</v>
+        <v>873</v>
       </c>
       <c r="C50" s="12" t="n">
         <v>0</v>
@@ -16161,11 +15621,11 @@
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>2011-07-17</t>
+          <t>2011-07-23</t>
         </is>
       </c>
       <c r="B51" s="12" t="n">
-        <v>577</v>
+        <v>744</v>
       </c>
       <c r="C51" s="12" t="n">
         <v>0</v>
@@ -16197,11 +15657,11 @@
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>2011-07-18</t>
+          <t>2011-07-24</t>
         </is>
       </c>
       <c r="B52" s="12" t="n">
-        <v>714</v>
+        <v>521</v>
       </c>
       <c r="C52" s="12" t="n">
         <v>0</v>
@@ -16233,11 +15693,11 @@
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>2011-07-19</t>
+          <t>2011-07-25</t>
         </is>
       </c>
       <c r="B53" s="12" t="n">
-        <v>953</v>
+        <v>572</v>
       </c>
       <c r="C53" s="12" t="n">
         <v>0</v>
@@ -16269,11 +15729,11 @@
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>2011-07-20</t>
+          <t>2011-07-26</t>
         </is>
       </c>
       <c r="B54" s="12" t="n">
-        <v>870</v>
+        <v>715</v>
       </c>
       <c r="C54" s="12" t="n">
         <v>0</v>
@@ -16305,11 +15765,11 @@
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>2011-07-21</t>
+          <t>2011-07-27</t>
         </is>
       </c>
       <c r="B55" s="12" t="n">
-        <v>727</v>
+        <v>850</v>
       </c>
       <c r="C55" s="12" t="n">
         <v>0</v>
@@ -16341,11 +15801,11 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>2011-07-22</t>
+          <t>2011-07-28</t>
         </is>
       </c>
       <c r="B56" s="12" t="n">
-        <v>873</v>
+        <v>920</v>
       </c>
       <c r="C56" s="12" t="n">
         <v>0</v>
@@ -16377,11 +15837,11 @@
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>2011-07-23</t>
+          <t>2011-07-29</t>
         </is>
       </c>
       <c r="B57" s="12" t="n">
-        <v>744</v>
+        <v>795</v>
       </c>
       <c r="C57" s="12" t="n">
         <v>0</v>
@@ -16413,11 +15873,11 @@
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>2011-07-24</t>
+          <t>2011-07-30</t>
         </is>
       </c>
       <c r="B58" s="12" t="n">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C58" s="12" t="n">
         <v>0</v>
@@ -16449,11 +15909,11 @@
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>2011-07-25</t>
+          <t>2011-07-31</t>
         </is>
       </c>
       <c r="B59" s="12" t="n">
-        <v>572</v>
+        <v>469</v>
       </c>
       <c r="C59" s="12" t="n">
         <v>0</v>
@@ -16485,11 +15945,11 @@
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>2011-07-26</t>
+          <t>2011-08-01</t>
         </is>
       </c>
       <c r="B60" s="12" t="n">
-        <v>715</v>
+        <v>1036</v>
       </c>
       <c r="C60" s="12" t="n">
         <v>0</v>
@@ -16521,11 +15981,11 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>2011-07-27</t>
+          <t>2011-08-02</t>
         </is>
       </c>
       <c r="B61" s="12" t="n">
-        <v>850</v>
+        <v>649</v>
       </c>
       <c r="C61" s="12" t="n">
         <v>0</v>
@@ -16557,11 +16017,11 @@
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>2011-07-28</t>
+          <t>2011-08-03</t>
         </is>
       </c>
       <c r="B62" s="12" t="n">
-        <v>920</v>
+        <v>863</v>
       </c>
       <c r="C62" s="12" t="n">
         <v>0</v>
@@ -16593,11 +16053,11 @@
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>2011-07-29</t>
+          <t>2011-08-04</t>
         </is>
       </c>
       <c r="B63" s="12" t="n">
-        <v>795</v>
+        <v>760</v>
       </c>
       <c r="C63" s="12" t="n">
         <v>0</v>
@@ -16629,11 +16089,11 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>2011-07-30</t>
+          <t>2011-08-05</t>
         </is>
       </c>
       <c r="B64" s="12" t="n">
-        <v>519</v>
+        <v>875</v>
       </c>
       <c r="C64" s="12" t="n">
         <v>0</v>
@@ -16665,11 +16125,11 @@
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>2011-07-31</t>
+          <t>2011-08-06</t>
         </is>
       </c>
       <c r="B65" s="12" t="n">
-        <v>469</v>
+        <v>639</v>
       </c>
       <c r="C65" s="12" t="n">
         <v>0</v>
@@ -16701,11 +16161,11 @@
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>2011-08-01</t>
+          <t>2011-08-07</t>
         </is>
       </c>
       <c r="B66" s="12" t="n">
-        <v>1036</v>
+        <v>699</v>
       </c>
       <c r="C66" s="12" t="n">
         <v>0</v>
@@ -16737,11 +16197,11 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>2011-08-02</t>
+          <t>2011-08-08</t>
         </is>
       </c>
       <c r="B67" s="12" t="n">
-        <v>649</v>
+        <v>1032</v>
       </c>
       <c r="C67" s="12" t="n">
         <v>0</v>
@@ -16773,11 +16233,11 @@
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>2011-08-03</t>
+          <t>2011-08-09</t>
         </is>
       </c>
       <c r="B68" s="12" t="n">
-        <v>863</v>
+        <v>1041</v>
       </c>
       <c r="C68" s="12" t="n">
         <v>0</v>
@@ -16809,11 +16269,11 @@
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>2011-08-04</t>
+          <t>2011-08-10</t>
         </is>
       </c>
       <c r="B69" s="12" t="n">
-        <v>760</v>
+        <v>974</v>
       </c>
       <c r="C69" s="12" t="n">
         <v>0</v>
@@ -16845,11 +16305,11 @@
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>2011-08-05</t>
+          <t>2011-08-11</t>
         </is>
       </c>
       <c r="B70" s="12" t="n">
-        <v>875</v>
+        <v>1084</v>
       </c>
       <c r="C70" s="12" t="n">
         <v>0</v>
@@ -16881,11 +16341,11 @@
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>2011-08-06</t>
+          <t>2011-08-12</t>
         </is>
       </c>
       <c r="B71" s="12" t="n">
-        <v>639</v>
+        <v>1151</v>
       </c>
       <c r="C71" s="12" t="n">
         <v>0</v>
@@ -16917,11 +16377,11 @@
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>2011-08-07</t>
+          <t>2011-08-13</t>
         </is>
       </c>
       <c r="B72" s="12" t="n">
-        <v>699</v>
+        <v>522</v>
       </c>
       <c r="C72" s="12" t="n">
         <v>0</v>
@@ -16953,11 +16413,11 @@
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>2011-08-08</t>
+          <t>2011-08-14</t>
         </is>
       </c>
       <c r="B73" s="12" t="n">
-        <v>1032</v>
+        <v>497</v>
       </c>
       <c r="C73" s="12" t="n">
         <v>0</v>
@@ -16987,17 +16447,9 @@
       <c r="Z73" s="3" t="n"/>
     </row>
     <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
-        <is>
-          <t>2011-08-09</t>
-        </is>
-      </c>
-      <c r="B74" s="12" t="n">
-        <v>1041</v>
-      </c>
-      <c r="C74" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="A74" s="3" t="n"/>
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="3" t="n"/>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="3" t="n"/>
       <c r="F74" s="3" t="n"/>
@@ -17023,17 +16475,9 @@
       <c r="Z74" s="3" t="n"/>
     </row>
     <row r="75" ht="22" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t>2011-08-10</t>
-        </is>
-      </c>
-      <c r="B75" s="12" t="n">
-        <v>974</v>
-      </c>
-      <c r="C75" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="A75" s="3" t="n"/>
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3" t="n"/>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="3" t="n"/>
       <c r="F75" s="3" t="n"/>
@@ -17059,17 +16503,9 @@
       <c r="Z75" s="3" t="n"/>
     </row>
     <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t>2011-08-11</t>
-        </is>
-      </c>
-      <c r="B76" s="12" t="n">
-        <v>1084</v>
-      </c>
-      <c r="C76" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="A76" s="3" t="n"/>
+      <c r="B76" s="3" t="n"/>
+      <c r="C76" s="3" t="n"/>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="3" t="n"/>
       <c r="F76" s="3" t="n"/>
@@ -17095,17 +16531,9 @@
       <c r="Z76" s="3" t="n"/>
     </row>
     <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t>2011-08-12</t>
-        </is>
-      </c>
-      <c r="B77" s="12" t="n">
-        <v>1151</v>
-      </c>
-      <c r="C77" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="A77" s="3" t="n"/>
+      <c r="B77" s="3" t="n"/>
+      <c r="C77" s="3" t="n"/>
       <c r="D77" s="3" t="n"/>
       <c r="E77" s="3" t="n"/>
       <c r="F77" s="3" t="n"/>
@@ -17131,17 +16559,9 @@
       <c r="Z77" s="3" t="n"/>
     </row>
     <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t>2011-08-13</t>
-        </is>
-      </c>
-      <c r="B78" s="12" t="n">
-        <v>522</v>
-      </c>
-      <c r="C78" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="A78" s="3" t="n"/>
+      <c r="B78" s="3" t="n"/>
+      <c r="C78" s="3" t="n"/>
       <c r="D78" s="3" t="n"/>
       <c r="E78" s="3" t="n"/>
       <c r="F78" s="3" t="n"/>
@@ -17167,17 +16587,9 @@
       <c r="Z78" s="3" t="n"/>
     </row>
     <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="11" t="inlineStr">
-        <is>
-          <t>2011-08-14</t>
-        </is>
-      </c>
-      <c r="B79" s="12" t="n">
-        <v>497</v>
-      </c>
-      <c r="C79" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="A79" s="3" t="n"/>
+      <c r="B79" s="3" t="n"/>
+      <c r="C79" s="3" t="n"/>
       <c r="D79" s="3" t="n"/>
       <c r="E79" s="3" t="n"/>
       <c r="F79" s="3" t="n"/>

--- a/saidas/painel_meliuz.xlsx
+++ b/saidas/painel_meliuz.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,7 +37,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0017365D"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0031583A"/>
       <sz val="13"/>
     </font>
     <font>
@@ -45,14 +50,14 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="0044546A"/>
+      <color rgb="0034423A"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0017365D"/>
+      <color rgb="0031583A"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -61,32 +66,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F8FB"/>
+        <fgColor rgb="00F5F7F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0017365D"/>
+        <fgColor rgb="00426F49"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00FCE4EF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
+        <fgColor rgb="00E7F1E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00548235"/>
+        <fgColor rgb="00FFF0C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -119,16 +119,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9E2F3"/>
+        <color rgb="00D8E3D8"/>
       </left>
       <right style="thin">
-        <color rgb="00D9E2F3"/>
+        <color rgb="00D8E3D8"/>
       </right>
       <top style="thin">
-        <color rgb="00D9E2F3"/>
+        <color rgb="00D8E3D8"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9E2F3"/>
+        <color rgb="00D8E3D8"/>
       </bottom>
     </border>
   </borders>
@@ -137,51 +137,51 @@
   </cellStyleXfs>
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -266,10 +266,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5334000" cy="2857500"/>
+    <ext cx="400050" cy="400050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -289,12 +289,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5334000" cy="2857500"/>
+    <ext cx="5429250" cy="2905125"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -312,6 +312,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5429250" cy="2905125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -319,12 +344,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4953000" cy="2714625"/>
+    <ext cx="400050" cy="400050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -346,7 +371,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4953000" cy="2714625"/>
@@ -367,6 +392,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -374,12 +424,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4953000" cy="2714625"/>
+    <ext cx="400050" cy="400050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -401,7 +451,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4953000" cy="2714625"/>
@@ -422,6 +472,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -429,12 +504,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4953000" cy="2714625"/>
+    <ext cx="400050" cy="400050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -456,7 +531,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4953000" cy="2714625"/>
@@ -467,6 +542,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="2714625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -800,10 +900,11 @@
     <col width="12" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dashboard de Testes A/B de Cashback</t>
+          <t xml:space="preserve">     Dashboard de Testes A/B de Cashback
+     Analise automatizada de testes de cashback</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -832,19 +933,19 @@
       <c r="Y1" s="3" t="n"/>
       <c r="Z1" s="3" t="n"/>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
       <c r="M2" s="3" t="n"/>
       <c r="N2" s="3" t="n"/>
       <c r="O2" s="3" t="n"/>
@@ -860,39 +961,19 @@
       <c r="Y2" s="3" t="n"/>
       <c r="Z2" s="3" t="n"/>
     </row>
-    <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Testes analisados
-3</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Lucro vencedor total
-R$ 726.050,00</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="7" t="n"/>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>Margem media
-5,41%</t>
-        </is>
-      </c>
-      <c r="H3" s="9" t="n"/>
-      <c r="I3" s="9" t="n"/>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>ROI medio
-129,46%</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="n"/>
-      <c r="L3" s="5" t="n"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
       <c r="N3" s="3" t="n"/>
       <c r="O3" s="3" t="n"/>
@@ -909,16 +990,36 @@
       <c r="Z3" s="3" t="n"/>
     </row>
     <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="5" t="n"/>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Testes analisados
+3</t>
+        </is>
+      </c>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="7" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Lucro vencedor total
+R$ 726.050,00</t>
+        </is>
+      </c>
       <c r="E4" s="7" t="n"/>
       <c r="F4" s="7" t="n"/>
-      <c r="G4" s="9" t="n"/>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Margem media
+5,41%</t>
+        </is>
+      </c>
       <c r="H4" s="9" t="n"/>
       <c r="I4" s="9" t="n"/>
-      <c r="J4" s="5" t="n"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>ROI medio
+129,46%</t>
+        </is>
+      </c>
       <c r="K4" s="5" t="n"/>
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="3" t="n"/>
@@ -964,19 +1065,19 @@
       <c r="Y5" s="3" t="n"/>
       <c r="Z5" s="3" t="n"/>
     </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="3" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="9" t="n"/>
+      <c r="I6" s="9" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
       <c r="M6" s="3" t="n"/>
       <c r="N6" s="3" t="n"/>
       <c r="O6" s="3" t="n"/>
@@ -1021,41 +1122,13 @@
       <c r="Z7" s="3" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Parceiro</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Periodo</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Variante</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Lucro</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>Margem</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>ROI</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>Decisao</t>
-        </is>
-      </c>
+      <c r="A8" s="3" t="n"/>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
@@ -1076,34 +1149,40 @@
       <c r="Y8" s="3" t="n"/>
       <c r="Z8" s="3" t="n"/>
     </row>
-    <row r="9" ht="38" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>Parceiro A</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>2011-01-01 a 2011-04-02</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Grupo 1</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>404711</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>0.07220312379296767</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>1.733802008362465</v>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>Escalar Grupo 1 para 100% do trafego, mantendo monitoramento de margem e cashback pago nos primeiros dias.</t>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Parceiro</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Periodo</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Variante</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Lucro</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Margem</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>ROI</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Decisao</t>
         </is>
       </c>
       <c r="H9" s="3" t="n"/>
@@ -1129,12 +1208,12 @@
     <row r="10" ht="38" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>Parceiro B</t>
+          <t>Parceiro A</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>2011-05-01 a 2011-06-30</t>
+          <t>2011-01-01 a 2011-04-02</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -1143,13 +1222,13 @@
         </is>
       </c>
       <c r="D10" s="12" t="n">
-        <v>286570</v>
+        <v>404711</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>0.07000066930185954</v>
+        <v>0.07220312379296767</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1.750035114289378</v>
+        <v>1.733802008362465</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1179,12 +1258,12 @@
     <row r="11" ht="38" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Parceiro C</t>
+          <t>Parceiro B</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>2011-07-01 a 2011-08-14</t>
+          <t>2011-05-01 a 2011-06-30</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1193,13 +1272,13 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>34769</v>
+        <v>286570</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>0.0199998849556504</v>
+        <v>0.07000066930185954</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.3999930974184345</v>
+        <v>1.750035114289378</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
@@ -1226,14 +1305,36 @@
       <c r="Y11" s="3" t="n"/>
       <c r="Z11" s="3" t="n"/>
     </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="3" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
+    <row r="12" ht="38" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Parceiro C</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>2011-07-01 a 2011-08-14</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>34769</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>0.0199998849556504</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>0.3999930974184345</v>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Escalar Grupo 1 para 100% do trafego, mantendo monitoramento de margem e cashback pago nos primeiros dias.</t>
+        </is>
+      </c>
       <c r="H12" s="3" t="n"/>
       <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="n"/>
@@ -4280,11 +4381,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="D3:F5"/>
-    <mergeCell ref="J3:L5"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="G3:I5"/>
-    <mergeCell ref="A3:C5"/>
+    <mergeCell ref="G4:I6"/>
+    <mergeCell ref="J4:L6"/>
+    <mergeCell ref="A1:L2"/>
+    <mergeCell ref="A4:C6"/>
+    <mergeCell ref="D4:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4328,10 +4429,11 @@
     <col width="12" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Teste cashback - Parceiro A</t>
+          <t xml:space="preserve">     Teste cashback - Parceiro A
+     2011-01-01 a 2011-04-02 | decisao automatizada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4364,21 +4466,21 @@
       <c r="Y1" s="3" t="n"/>
       <c r="Z1" s="3" t="n"/>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
-      <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3" t="n"/>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
       <c r="O2" s="3" t="n"/>
       <c r="P2" s="3" t="n"/>
       <c r="Q2" s="3" t="n"/>
@@ -4392,35 +4494,15 @@
       <c r="Y2" s="3" t="n"/>
       <c r="Z2" s="3" t="n"/>
     </row>
-    <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Variante recomendada
-Grupo 1</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Lucro liquido
-R$ 404.711,00</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>Margem GMV
-7,22%</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="n"/>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>ROI cashback
-173,38%</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="n"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
@@ -4457,13 +4539,33 @@
       <c r="Z3" s="3" t="n"/>
     </row>
     <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="7" t="n"/>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Variante recomendada
+Grupo 1</t>
+        </is>
+      </c>
       <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Lucro liquido
+R$ 404.711,00</t>
+        </is>
+      </c>
       <c r="D4" s="7" t="n"/>
-      <c r="E4" s="9" t="n"/>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Margem GMV
+7,22%</t>
+        </is>
+      </c>
       <c r="F4" s="9" t="n"/>
-      <c r="G4" s="5" t="n"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>ROI cashback
+173,38%</t>
+        </is>
+      </c>
       <c r="H4" s="5" t="n"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
@@ -4532,15 +4634,15 @@
       <c r="Y5" s="3" t="n"/>
       <c r="Z5" s="3" t="n"/>
     </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="3" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
       <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
@@ -4571,22 +4673,14 @@
       <c r="Z6" s="3" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>Decisao</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Escalar Grupo 1 para 100% do trafego, mantendo monitoramento de margem e cashback pago nos primeiros dias.</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="18" t="n"/>
-      <c r="E7" s="18" t="n"/>
-      <c r="F7" s="18" t="n"/>
-      <c r="G7" s="18" t="n"/>
-      <c r="H7" s="18" t="n"/>
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n"/>
@@ -4617,8 +4711,16 @@
       <c r="Z7" s="3" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="18" t="n"/>
-      <c r="B8" s="18" t="n"/>
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Decisao</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Escalar Grupo 1 para 100% do trafego, mantendo monitoramento de margem e cashback pago nos primeiros dias.</t>
+        </is>
+      </c>
       <c r="C8" s="18" t="n"/>
       <c r="D8" s="18" t="n"/>
       <c r="E8" s="18" t="n"/>
@@ -4655,14 +4757,14 @@
       <c r="Z8" s="3" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
+      <c r="A9" s="18" t="n"/>
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="n"/>
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="n"/>
@@ -4731,46 +4833,14 @@
       <c r="Z10" s="3" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Grupo</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Compradores</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>GMV</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Cashback</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>Lucro</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>Margem</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>ROI</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Ticket medio</t>
-        </is>
-      </c>
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="n"/>
@@ -4801,31 +4871,45 @@
       <c r="Z11" s="3" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>Grupo 1</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="n">
-        <v>9633</v>
-      </c>
-      <c r="C12" s="20" t="n">
-        <v>5605173</v>
-      </c>
-      <c r="D12" s="20" t="n">
-        <v>233424</v>
-      </c>
-      <c r="E12" s="20" t="n">
-        <v>404711</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>0.07220312379296767</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>1.733802008362465</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>581.8720024914356</v>
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Compradores</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>GMV</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Cashback</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Lucro</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Margem</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>ROI</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>Ticket medio</t>
+        </is>
       </c>
       <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="n"/>
@@ -4857,31 +4941,31 @@
       <c r="Z12" s="3" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Grupo 2</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="n">
-        <v>10814</v>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>6423096</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>370659</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>357519</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>0.05566147540064791</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>0.9645496264760872</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>593.9611614573701</v>
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>9633</v>
+      </c>
+      <c r="C13" s="20" t="n">
+        <v>5605173</v>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>233424</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>404711</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>0.07220312379296767</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>1.733802008362465</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>581.8720024914356</v>
       </c>
       <c r="I13" s="3" t="n"/>
       <c r="J13" s="3" t="n"/>
@@ -4915,29 +4999,29 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 2</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>11410</v>
+        <v>10814</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>6785856</v>
+        <v>6423096</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>503600</v>
+        <v>370659</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>264287</v>
+        <v>357519</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.03894674452272492</v>
+        <v>0.05566147540064791</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>0.5247954725972994</v>
+        <v>0.9645496264760872</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>594.7288343558282</v>
+        <v>593.9611614573701</v>
       </c>
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
@@ -4969,14 +5053,32 @@
       <c r="Z14" s="3" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>11410</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>6785856</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>503600</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>264287</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>0.03894674452272492</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>0.5247954725972994</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>594.7288343558282</v>
+      </c>
       <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="n"/>
@@ -8748,12 +8850,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A3:B5"/>
-    <mergeCell ref="G3:H5"/>
-    <mergeCell ref="E3:F5"/>
-    <mergeCell ref="B7:H8"/>
-    <mergeCell ref="C3:D5"/>
+    <mergeCell ref="A1:N2"/>
+    <mergeCell ref="E4:F6"/>
+    <mergeCell ref="B8:H9"/>
+    <mergeCell ref="C4:D6"/>
+    <mergeCell ref="A4:B6"/>
+    <mergeCell ref="G4:H6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8797,10 +8899,11 @@
     <col width="12" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Teste cashback - Parceiro B</t>
+          <t xml:space="preserve">     Teste cashback - Parceiro B
+     2011-05-01 a 2011-06-30 | decisao automatizada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8833,21 +8936,21 @@
       <c r="Y1" s="3" t="n"/>
       <c r="Z1" s="3" t="n"/>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
-      <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3" t="n"/>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
       <c r="O2" s="3" t="n"/>
       <c r="P2" s="3" t="n"/>
       <c r="Q2" s="3" t="n"/>
@@ -8861,35 +8964,15 @@
       <c r="Y2" s="3" t="n"/>
       <c r="Z2" s="3" t="n"/>
     </row>
-    <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Variante recomendada
-Grupo 1</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Lucro liquido
-R$ 286.570,00</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>Margem GMV
-7,00%</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="n"/>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>ROI cashback
-175,00%</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="n"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
@@ -8926,13 +9009,33 @@
       <c r="Z3" s="3" t="n"/>
     </row>
     <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="7" t="n"/>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Variante recomendada
+Grupo 1</t>
+        </is>
+      </c>
       <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Lucro liquido
+R$ 286.570,00</t>
+        </is>
+      </c>
       <c r="D4" s="7" t="n"/>
-      <c r="E4" s="9" t="n"/>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Margem GMV
+7,00%</t>
+        </is>
+      </c>
       <c r="F4" s="9" t="n"/>
-      <c r="G4" s="5" t="n"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>ROI cashback
+175,00%</t>
+        </is>
+      </c>
       <c r="H4" s="5" t="n"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
@@ -9001,15 +9104,15 @@
       <c r="Y5" s="3" t="n"/>
       <c r="Z5" s="3" t="n"/>
     </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="3" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
       <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
@@ -9040,22 +9143,14 @@
       <c r="Z6" s="3" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>Decisao</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Escalar Grupo 1 para 100% do trafego, mantendo monitoramento de margem e cashback pago nos primeiros dias.</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="18" t="n"/>
-      <c r="E7" s="18" t="n"/>
-      <c r="F7" s="18" t="n"/>
-      <c r="G7" s="18" t="n"/>
-      <c r="H7" s="18" t="n"/>
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n"/>
@@ -9086,8 +9181,16 @@
       <c r="Z7" s="3" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="18" t="n"/>
-      <c r="B8" s="18" t="n"/>
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Decisao</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Escalar Grupo 1 para 100% do trafego, mantendo monitoramento de margem e cashback pago nos primeiros dias.</t>
+        </is>
+      </c>
       <c r="C8" s="18" t="n"/>
       <c r="D8" s="18" t="n"/>
       <c r="E8" s="18" t="n"/>
@@ -9124,14 +9227,14 @@
       <c r="Z8" s="3" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
+      <c r="A9" s="18" t="n"/>
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="n"/>
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="n"/>
@@ -9200,46 +9303,14 @@
       <c r="Z10" s="3" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Grupo</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Compradores</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>GMV</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Cashback</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>Lucro</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>Margem</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>ROI</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Ticket medio</t>
-        </is>
-      </c>
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="n"/>
@@ -9270,31 +9341,45 @@
       <c r="Z11" s="3" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>Grupo 1</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="n">
-        <v>7990</v>
-      </c>
-      <c r="C12" s="20" t="n">
-        <v>4093818</v>
-      </c>
-      <c r="D12" s="20" t="n">
-        <v>163751</v>
-      </c>
-      <c r="E12" s="20" t="n">
-        <v>286570</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>0.07000066930185954</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>1.750035114289378</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>512.3677096370463</v>
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Compradores</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>GMV</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Cashback</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Lucro</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Margem</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>ROI</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>Ticket medio</t>
+        </is>
       </c>
       <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="n"/>
@@ -9326,31 +9411,31 @@
       <c r="Z12" s="3" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Grupo 2</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="n">
-        <v>5452</v>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>2863019</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>171778</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>143157</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>0.05000211315398186</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>0.8333837860494359</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>525.1318782098313</v>
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>7990</v>
+      </c>
+      <c r="C13" s="20" t="n">
+        <v>4093818</v>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>163751</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>286570</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>0.07000066930185954</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>1.750035114289378</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>512.3677096370463</v>
       </c>
       <c r="I13" s="3" t="n"/>
       <c r="J13" s="3" t="n"/>
@@ -9384,29 +9469,29 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 2</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>5029</v>
+        <v>5452</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>2629963</v>
+        <v>2863019</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>236697</v>
+        <v>171778</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>52593</v>
+        <v>143157</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.01999761973837655</v>
+        <v>0.05000211315398186</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>0.2221954650882774</v>
+        <v>0.8333837860494359</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>522.9594352754027</v>
+        <v>525.1318782098313</v>
       </c>
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
@@ -9438,14 +9523,32 @@
       <c r="Z14" s="3" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>5029</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>2629963</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>236697</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>52593</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>0.01999761973837655</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>0.2221954650882774</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>522.9594352754027</v>
+      </c>
       <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="n"/>
@@ -12907,12 +13010,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A3:B5"/>
-    <mergeCell ref="G3:H5"/>
-    <mergeCell ref="E3:F5"/>
-    <mergeCell ref="B7:H8"/>
-    <mergeCell ref="C3:D5"/>
+    <mergeCell ref="A1:N2"/>
+    <mergeCell ref="E4:F6"/>
+    <mergeCell ref="B8:H9"/>
+    <mergeCell ref="C4:D6"/>
+    <mergeCell ref="A4:B6"/>
+    <mergeCell ref="G4:H6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -12956,10 +13059,11 @@
     <col width="12" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Teste cashback - Parceiro C</t>
+          <t xml:space="preserve">     Teste cashback - Parceiro C
+     2011-07-01 a 2011-08-14 | decisao automatizada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -12992,21 +13096,21 @@
       <c r="Y1" s="3" t="n"/>
       <c r="Z1" s="3" t="n"/>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
-      <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3" t="n"/>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
       <c r="O2" s="3" t="n"/>
       <c r="P2" s="3" t="n"/>
       <c r="Q2" s="3" t="n"/>
@@ -13020,35 +13124,15 @@
       <c r="Y2" s="3" t="n"/>
       <c r="Z2" s="3" t="n"/>
     </row>
-    <row r="3" ht="27" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Variante recomendada
-Grupo 1</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Lucro liquido
-R$ 34.769,00</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>Margem GMV
-2,00%</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="n"/>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>ROI cashback
-40,00%</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="n"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
@@ -13081,13 +13165,33 @@
       <c r="Z3" s="3" t="n"/>
     </row>
     <row r="4" ht="27" customHeight="1">
-      <c r="A4" s="7" t="n"/>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Variante recomendada
+Grupo 1</t>
+        </is>
+      </c>
       <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Lucro liquido
+R$ 34.769,00</t>
+        </is>
+      </c>
       <c r="D4" s="7" t="n"/>
-      <c r="E4" s="9" t="n"/>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Margem GMV
+2,00%</t>
+        </is>
+      </c>
       <c r="F4" s="9" t="n"/>
-      <c r="G4" s="5" t="n"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>ROI cashback
+40,00%</t>
+        </is>
+      </c>
       <c r="H4" s="5" t="n"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
@@ -13152,15 +13256,15 @@
       <c r="Y5" s="3" t="n"/>
       <c r="Z5" s="3" t="n"/>
     </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="3" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
       <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
@@ -13189,22 +13293,14 @@
       <c r="Z6" s="3" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>Decisao</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Escalar Grupo 1 para 100% do trafego, mantendo monitoramento de margem e cashback pago nos primeiros dias.</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="18" t="n"/>
-      <c r="E7" s="18" t="n"/>
-      <c r="F7" s="18" t="n"/>
-      <c r="G7" s="18" t="n"/>
-      <c r="H7" s="18" t="n"/>
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n"/>
@@ -13233,8 +13329,16 @@
       <c r="Z7" s="3" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="18" t="n"/>
-      <c r="B8" s="18" t="n"/>
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Decisao</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Escalar Grupo 1 para 100% do trafego, mantendo monitoramento de margem e cashback pago nos primeiros dias.</t>
+        </is>
+      </c>
       <c r="C8" s="18" t="n"/>
       <c r="D8" s="18" t="n"/>
       <c r="E8" s="18" t="n"/>
@@ -13269,14 +13373,14 @@
       <c r="Z8" s="3" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
+      <c r="A9" s="18" t="n"/>
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="n"/>
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="n"/>
@@ -13341,46 +13445,14 @@
       <c r="Z10" s="3" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Grupo</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Compradores</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>GMV</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Cashback</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>Lucro</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>Margem</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>ROI</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Ticket medio</t>
-        </is>
-      </c>
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="n"/>
@@ -13409,31 +13481,45 @@
       <c r="Z11" s="3" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>Grupo 1</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="n">
-        <v>4549</v>
-      </c>
-      <c r="C12" s="20" t="n">
-        <v>1738460</v>
-      </c>
-      <c r="D12" s="20" t="n">
-        <v>86924</v>
-      </c>
-      <c r="E12" s="20" t="n">
-        <v>34769</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>0.0199998849556504</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>0.3999930974184345</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>382.1631127720378</v>
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Compradores</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>GMV</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Cashback</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Lucro</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Margem</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>ROI</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>Ticket medio</t>
+        </is>
       </c>
       <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="n"/>
@@ -13463,31 +13549,31 @@
       <c r="Z12" s="3" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Grupo 2</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="n">
-        <v>4522</v>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>1685235</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>117967</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>372.6747014595312</v>
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>4549</v>
+      </c>
+      <c r="C13" s="20" t="n">
+        <v>1738460</v>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>86924</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>34769</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>0.0199998849556504</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>0.3999930974184345</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>382.1631127720378</v>
       </c>
       <c r="I13" s="3" t="n"/>
       <c r="J13" s="3" t="n"/>
@@ -13517,14 +13603,32 @@
       <c r="Z13" s="3" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="3" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Grupo 2</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>4522</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>1685235</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>117967</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>372.6747014595312</v>
+      </c>
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="n"/>
@@ -16794,12 +16898,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A3:B5"/>
-    <mergeCell ref="G3:H5"/>
-    <mergeCell ref="E3:F5"/>
-    <mergeCell ref="B7:H8"/>
-    <mergeCell ref="C3:D5"/>
+    <mergeCell ref="A1:N2"/>
+    <mergeCell ref="E4:F6"/>
+    <mergeCell ref="B8:H9"/>
+    <mergeCell ref="C4:D6"/>
+    <mergeCell ref="A4:B6"/>
+    <mergeCell ref="G4:H6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
